--- a/flatfile_templates/prebuilt_templates/v3.0/NG911_GISDataModelSchemaReport_v3.0.xlsx
+++ b/flatfile_templates/prebuilt_templates/v3.0/NG911_GISDataModelSchemaReport_v3.0.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domains" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section 4 Layer Overview" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section 5 Fields Overview" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Section 7.1 Layer Registry" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIS Layer Registry" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,10 +76,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -11529,8 +11529,8 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="100" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11571,9 +11571,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A case-sensitive alphanumeric code of up to six characters used to disambiguate addresses in Canada.
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A case-sensitive alphanumeric code of up to six characters, used to disambiguate addresses in Canada.
 </t>
         </is>
       </c>
@@ -11605,1149 +11605,1149 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t>AddressNumber</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>RANGE</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The integer identifier of a location along a thoroughfare or within a defined community.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>999999</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>AdministrativeLevels0</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The name of a country represented by its two letter ISO 3166-1 English country alpha-2 code elements in UPPERCASE letters.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>AdministrativeLevels1</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The name of a state, province, or territory represented by the two-letter UPPERCASE abbreviation given in ISO 3166-2.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Alberta</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>American Samoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>District of Columbia</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FM</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Federated States of Micronesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GU</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Guam</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Marshall Islands</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>New Brunswick</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Newfoundland and Labrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Nova Scotia</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Northern Mariana Islands</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Northwest Territories</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Nunavut</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Prince Edward Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PW</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Palau</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>RI</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UM</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>United States Minor Outlying Islands</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Virgin Islands</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>WV</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>YT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Yukon</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>AdministrativeLevels2</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The name of the primary subdivision of a state, province, or territory.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>User Defined</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>User Defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>AdministrativeLevels3</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The name of the secondary division of a state, province, or territory. In Canada, where no Administrative Level 2 exists, it can be the name of the primary division of the province or territory.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>User Defined</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>User Defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
           <t>AgencyID</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>CODED</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A Domain Name System (DNS) domain name which is used to uniquely identify an agency.
 </t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>User Defined</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>User Defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>AddressNumber</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>RANGE</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The numeric identifier of a location along a thoroughfare or within a defined community.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>999999</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>AdministrativeLevels0</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The name of a country represented by its two-letter ISO 3166-1 English country alpha-2 code elements in UPPER CASE letters.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>AdministrativeLevels1</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The name of a state or state equivalent, represented by the two-letter abbreviation given in USPS Publication 28, Appendix B.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Alberta</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Alabama</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>AK</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>AS</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>American Samoa</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Arkansas</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>British Columbia</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Colorado</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Connecticut</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Delaware</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>District of Columbia</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>FM</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Federated States of Micronesia</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Georgia</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>GU</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Guam</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>HI</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Idaho</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Illinois</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>IA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>KS</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Louisiana</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Manitoba</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Maine</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Marshall Islands</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MN</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Minnesota</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Mississippi</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Missouri</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Montana</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>NB</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>New Brunswick</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Newfoundland and Labrador</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nova Scotia</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Nevada</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>New Hampshire</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>NM</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>ND</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>North Dakota</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MP</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Northern Mariana Islands</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Northwest Territories</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Nunavut</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OH</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ontario</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>PE</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Prince Edward Island</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>PW</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Palau</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Puerto Rico</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Quebec</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>RI</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Saskatchewan</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Texas</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>UT</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>VT</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Vermont</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>UM</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>United States Minor Outlying Islands</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Virgin Islands</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Washington</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>WV</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>West Virginia</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>WI</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>YT</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Yukon</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>AdministrativeLevels2</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The name of a County or County-equivalent where the address is located. The Domain is restricted to the exact listed values as published in ANSI INCITS 31:2009, including casing and use of abbreviations.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>User Defined</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>User Defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>AdministrativeLevels3</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The name of the secondary division of a state, province, or territory. In Canada, where no Administrative Level 2 exists, it can be the name of the primary division of the province or territory.
-</t>
-        </is>
-      </c>
-    </row>
     <row r="101">
       <c r="B101" s="1" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicator of the type of distance marker.
 </t>
@@ -12847,7 +12847,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Unit of measurement used for the distance marker.
 </t>
@@ -12942,9 +12942,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A 3-5 character alphanumeric string that represents an Emergency Service Zone (ESZ).
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A 3-5 character numeric string that represents one or more Emergency Service Zones (ESZ).
 </t>
         </is>
       </c>
@@ -12989,7 +12989,7 @@
           <t>REAL</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The angular distance of a location north or south of the equator as defined by the coordinate system, expressed in decimal degrees.
 </t>
@@ -13036,9 +13036,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The street direction as it currently exists in the MSAG.
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The leading or trailing street direction suffix as it currently exists in the MSAG.
 </t>
         </is>
       </c>
@@ -13190,22 +13190,22 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>LocationMarkerIndicator</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>RANGE</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>REAL</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The angular distance of a location east or west of the prime meridian of the coordinate system, expressed in decimal degrees..
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicates whether the location marker is identified by a physical sign.
 </t>
         </is>
       </c>
@@ -13213,83 +13213,83 @@
     <row r="140">
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t>-180.0</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>LocationMarkerIndicator</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indicates whether the location marker is identified by a physical sign.
+          <t>Posted</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Unposted</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>RANGE</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The angular distance of a location east or west of the prime meridian of the coordinate system, expressed in decimal degrees.
 </t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="B144" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
     <row r="145">
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Posted</t>
+      <c r="B145" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>-180.0</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Unposted</t>
+          <t>180.0</t>
         </is>
       </c>
     </row>
@@ -13309,7 +13309,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="D148" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The direction of traffic movement along a road in relation to the FROM node and TO node of the line segment representing the road in the GIS data.
 </t>
@@ -13380,9 +13380,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The even or odd property of the address number on the corresponding side of the road segment relative to the FROM Node.
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The even or odd property of the address number range of the road segment relative to the FROM Node.
 </t>
         </is>
       </c>
@@ -13463,7 +13463,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D161" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The methodology used for placement of the address point.
 </t>
@@ -13606,9 +13606,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The methodology used for placement of the address polygon.
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The methodology defining the extent of an address polygon.
 </t>
         </is>
       </c>
@@ -13701,7 +13701,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D181" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The type of feature identified by the address.
 </t>
@@ -14312,9 +14312,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D232" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A system of 5-digit (US) or 7-character codes (Canada) that identify the individual USPS or Canadian Post Office or metropolitan area delivery station associated with an address.
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A system of codes that identifies an individual Post Office or metropolitan area delivery station associated with an address.
 </t>
         </is>
       </c>
@@ -14359,9 +14359,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D236" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A city name for the Postal Code of an address. 
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A mailing place name for the Postal Code of an address.
 </t>
         </is>
       </c>
@@ -14406,7 +14406,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D240" s="6" t="inlineStr">
+      <c r="D240" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The general description of the type of road.
 </t>
@@ -14597,9 +14597,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D256" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">URI for call routing. This attribute is contained in the service boundary layers and will define the Service URI of the service.
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">URI for call routing. This attribute is contained in the service boundary layers and will define the URI of the service.
 </t>
         </is>
       </c>
@@ -14644,9 +14644,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D260" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The URN used to select the service for which a route is desired.
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The SOS Service URN used to select the service for which a route is desired.
 </t>
         </is>
       </c>
@@ -14727,9 +14727,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D267" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The URN used to select the service for which a route is desired.
+      <c r="D267" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Responder Service URN used to select the service for which a route is desired.
 </t>
         </is>
       </c>
@@ -15242,9 +15242,9 @@
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="D310" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Posted Speed Limit in MPH in US or Km/h in Canada
+      <c r="D310" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Posted Speed Limit in MPH or Km/h.
 </t>
         </is>
       </c>
@@ -15289,9 +15289,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D314" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A word preceding or following the Street Name element that indicates the direction taken by the road from an arbitrary starting point or line, or the sector where it is located.
+      <c r="D314" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A word preceding or following the Street Name element that indicates the direction taken by the thoroughfare from an arbitrary starting point or line, or the sector where it is located.
 </t>
         </is>
       </c>
@@ -15516,7 +15516,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D333" s="6" t="inlineStr">
+      <c r="D333" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A word or phrase that precedes or follows the Street Name element and identifies a type of thoroughfare in a complete street name.
 </t>
@@ -20219,7 +20219,7 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D725" s="6" t="inlineStr">
+      <c r="D725" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A preposition or prepositional phrase between the Street Name Pre Type and the Street Name.
 </t>
@@ -20398,9 +20398,9 @@
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D740" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indicates if the address range on the corresponding side of the road segment should be used for civic location validation.
+      <c r="D740" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicates if the address range of the road segment, relative to the FROM node, should be used for civic location validation.
 </t>
         </is>
       </c>
@@ -20518,25 +20518,25 @@
           <t>RoadCenterLine</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>4.1.1</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>POLYLINE</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Roads data is maintained as a line layer for representing the centerline of a roadway. This dataset is referred to as the RoadCenterLine layer in the GIS Data Layers and Indicators registry in Section 7.1 “GIS Data Layers” Registry “GIS Layers and Indicators” Registry and in NENA documents going forward. GIS road centerline arc node topology is associated with attribute data containing information on street names, address ranges, jurisdictional boundaries, and other attributes. The RoadCenterLine layer is an integral part of any public safety GIS due to its versatility and use for:
 •	Querying and geocoding of civic addresses based on dual (left/right) address ranges
@@ -20567,25 +20567,25 @@
           <t>SiteStructureAddressPoint</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>4.2.1</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>POINT</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Site/Structure Addresses data is maintained as a point layer that supports 3D for representing the location of a site, a structure, an interior space, or access to a site, structure, or an interior space. This dataset is referred to as the SiteStructureAddressPoint layer in in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.  While the SiteStructureAddressPoint layer is required, there is no requirement for the completeness of these data. It is understood that it will take time and resources to develop complete and accurate Site/Structure Addresses data.
 Site/Structure Addresses data can be used to locate sites that otherwise may not geocode correctly using the road centerline data. It can also be used to locate areas of unusual addressing (i.e., odd addresses on the even side of the road centerlines and vice versa), and other areas where the data is available. Some addressable locations may be problematic near boundaries.
@@ -20611,25 +20611,25 @@
           <t>SiteStructureAddressPolygon</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>4.2.2</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Site/Structure Addresses data is maintained as a polygon layer to represent the extent of addressable areas such as outdoor sites, structures, or interior spaces. This dataset is referred to as the SiteStructureAddressPolygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. It is understood that it will take time and resources to fully develop complete and accurate Site/Structure Addresses data.
 Site/Structure Address Polygon data can be used to more effectively convert geodetic locations into civic locations than Site/Structure Address Point data. This is because the polygon represents the extent of the space whereas the point provides no information as to its extent. Gaps and overlaps between SiteStructureAddressPolygon features MAY exist and are permissible (e.g., a room on a floor within a building may be represented as three overlapping SiteStructureAddressPolygon features).
@@ -20655,25 +20655,25 @@
           <t>PsapPolygon</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>4.3.1</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In an NG9-1-1 deployment, the initial routing of a 9-1-1 call cannot happen without Primary PSAP boundaries. It is the most critical layer and MUST be provided. Its data structure is the same as all service boundary layers defined in this section. All polygons in this layer MUST have a Service URN of urn:service:sos.
 The PsapPolygon layer may have one or many PSAP Boundaries contained in the layer. Each PSAP Boundary defines the geographic area of a PSAP that has primary responsibilities for an emergency request. This layer is used by the ECRF to perform a geographic query to determine the PSAP to which an emergency request is routed. An emergency request is routed using the NG9-1-1 Core Services based upon the geographic location of the request, provided by either a civic address, geographic coordinate, or geodetic shapes as defined in NENA-STA-010.
@@ -20697,25 +20697,25 @@
           <t>PolicePolygon</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>4.3.2</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In an NG9-1-1 deployment, the selective transfer of 9-1-1 calls and Emergency Incident Data Objects (EIDOs) to another PSAP or downstream agency uses service boundary layers, all with the same data structure.
 The following layers (formerly known as Emergency Service Boundaries), which may be maintained as separate or combined, are the next highest priority for NG9-1-1 deployment. Primary Emergency Services MUST include the following:
@@ -20744,25 +20744,25 @@
           <t>FirePolygon</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>4.3.2</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In an NG9-1-1 deployment, the selective transfer of 9-1-1 calls and Emergency Incident Data Objects (EIDOs) to another PSAP or downstream agency uses service boundary layers, all with the same data structure.
 The following layers (formerly known as Emergency Service Boundaries), which may be maintained as separate or combined, are the next highest priority for NG9-1-1 deployment. Primary Emergency Services MUST include the following:
@@ -20791,25 +20791,25 @@
           <t>EmsPolygon</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>4.3.2</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In an NG9-1-1 deployment, the selective transfer of 9-1-1 calls and Emergency Incident Data Objects (EIDOs) to another PSAP or downstream agency uses service boundary layers, all with the same data structure.
 The following layers (formerly known as Emergency Service Boundaries), which may be maintained as separate or combined, are the next highest priority for NG9-1-1 deployment. Primary Emergency Services MUST include the following:
@@ -20838,25 +20838,25 @@
           <t>ServiceBoundaryPolygon</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>4.3.3</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In an NG9-1-1 deployment, the transfer of 9-1-1 calls uses service boundary layers, all with the same data structure. These agencies may be served by a call center, dispatch center, or other terms.
 Other service boundary layers, which may be maintained as separate or combined, MAY include, but are not limited to:
@@ -20884,23 +20884,23 @@
           <t>ProvisioningPolygon</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>4.4</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Provisioning Boundaries data is maintained as a polygon layer for representing the area of GIS data provisioning responsibility, with no unintentional gaps or overlaps. This dataset is commonly referred to as the ProvisioningPolygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. The Provisioning Boundary MUST align with data from all adjoining GIS Data Providers.
 A Provisioning Boundary can take on a variety of shapes; for example, it may represent the extent of a city, the extent of a county, a region with multiple cities and counties, or possibly the extent of all areas served by a particular PSAP.
@@ -20926,25 +20926,25 @@
           <t>A1Polygon</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>4.5.1</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrative Level 1 data, formerly States or Equivalents (A1) data, is maintained as a polygon layer for representing the geographic area of a state, province, territory, or other top level subdivision of the larger country corresponding to the PIDF LO A1 element. This dataset is referred to as the A1Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
 </t>
@@ -20967,25 +20967,25 @@
           <t>A2Polygon</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>4.5.2</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrative Level 2 data, formerly Counties or Equivalents (A2) data, is maintained as a polygon layer. It typically represents the geographic area of a county, parish, regional district, or other similar level division corresponding to the PIDF LO A2 element. The presence of A2 polygon records is conditional based on the CLDXF Standard applicable to their country. This dataset is referred to as the A2Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
 </t>
@@ -21008,25 +21008,25 @@
           <t>A3Polygon</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>4.5.3</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrative Level 3 data, formerly Incorporated Municipalities (A3) data, is maintained as a polygon layer. It typically represents the geographic area of a city, town, village, or other similar level division corresponding to the PIDF LO A3 element. The presence of A3 polygon records is conditional based on the CLDXF Standard applicable to their country. This dataset is referred to as the A3Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
 </t>
@@ -21049,25 +21049,25 @@
           <t>A4Polygon</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>4.5.4</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrative Level 4 data, formerly Unincorporated Communities (A4) data, is maintained as a polygon layer. It typically represents the geographic area of an unincorporated community, borough, ward, or other similar level division corresponding to the PIDF LO A4 element. The presence of A4 polygon records is conditional based on the CLDXF Standard applicable to their country. This dataset is referred to as the A4Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
 </t>
@@ -21090,25 +21090,25 @@
           <t>A5Polygon</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>4.5.5</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrative Level 5 data, formerly Neighborhood Communities (A5) data, is maintained as a polygon layer. It typically represents the geographic area of a neighborhood, commercial area, or other similar level division corresponding to the PIDF LO A5 element. The presence of A5 polygon records is conditional based on the CLDXF Standard applicable to their country. This dataset is referred to as the A5Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
 </t>
@@ -21131,23 +21131,23 @@
           <t>RailroadCenterLine</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="8" t="n">
         <v>4.6</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>POLYLINE</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Railroads data is maintained as a line layer for representing the centerline of a real world rail line. This dataset is referred to as the RailroadCenterLine layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Federal Railroad Administration’s Rail Lines database is in Appendix A of NENA-STA-006. A database structure crosswalk between this model and Canada’s National Railway Network database is in Appendix B of NENA-STA-006.
 </t>
@@ -21170,25 +21170,25 @@
           <t>HydrologyLine</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>4.7.1</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>POLYLINE</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Hydrology data is maintained as a line layer for representing creeks, streams, rivers, and other linear water features. This dataset is referred to as the HydrologyLine layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Geological Survey’s National Hydrography Dataset (NHD) database is in Appendix C of NENA-STA-006. A database structure crosswalk between this model and Canada’s National Hydrographic Network database is in Appendix D of NENA-STA-006.
 </t>
@@ -21211,25 +21211,25 @@
           <t>HydrologyPolygon</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>4.7.2</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>POLYGON</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Hydrology data is maintained as a polygon layer for representing areal water body features. This dataset is referred to as the HydrologyPolygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Geological Survey’s National Hydrography Dataset (NHD) database is in Appendix C of NENA-STA-006. A database structure crosswalk between this model and Canada’s National Hydrographic Network database is in Appendix D of NENA-STA-006.
 </t>
@@ -21252,23 +21252,23 @@
           <t>DistanceMarkerPoint</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>POINT</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Distance Markers data is maintained as a point layer and is used primarily for map display purposes. If required for ECRF and LVF purposes, Distance Markers data MUST be included in the SiteStructureAddressPoint layer. Distance Markers may represent a numeric measurement of a point along a route, such as a mile marker. This dataset is referred to as the DistanceMarkerPoint layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
 </t>
@@ -21291,23 +21291,23 @@
           <t>LocationMarkerPoint</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="8" t="n">
         <v>4.9</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>POINT</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Location Markers data is maintained as a point layer and is used primarily for map display purposes. If required for ECRF and LVF purposes, Location Markers data MUST be included in the SiteStructureAddressPoint layer. Location Markers may represent locations such as an alarm box, a utility pole, a callbox, trail intersection, buoy, channel marker, or other similar feature. This dataset is referred to as the LocationMarkerPoint layer in in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
 </t>
@@ -21413,7 +21413,7 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A case-sensitive alphanumeric code of up to six characters, used to disambiguate addresses in Canada when the combination of Administrative Level 2, Administrative Level 3, Administrative Level 4 (if used), and Street Name may not be unique within a province or territory.
 Domain: None
@@ -21422,28 +21422,28 @@
 </t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="n">
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I2" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="7" t="b">
+      <c r="I2" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21463,7 +21463,7 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Additional Code on the left side of the road segment relative to the FROM Node.
 Domain: None 
@@ -21472,28 +21472,28 @@
 </t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="7" t="b">
+      <c r="I3" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21513,7 +21513,7 @@
           <t>5.3</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Additional Code on the right side of the road segment relative to the FROM Node.
 Domain: None 
@@ -21522,28 +21522,28 @@
 </t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="b">
+      <c r="I4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21563,7 +21563,7 @@
           <t>5.4</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">URI(s) for additional data associated with the address. This attribute is contained in the SiteStructureAddressPoint and SiteStructureAddressPolygon layers and will define the URI of additional information about a location, including building information (blueprints, contact info, floor plans, etc.).
 Domain: None
@@ -21571,28 +21571,28 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7" t="b">
+      <c r="I5" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Information that relates to location but does not meet the definition of any other named location elements.
 Domain: None
@@ -21621,28 +21621,28 @@
 </t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>225</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7" t="b">
+      <c r="I6" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21662,7 +21662,7 @@
           <t>5.6</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The integer identifier of a location along a thoroughfare or within a defined community.
 Domain: None 
@@ -21671,30 +21671,30 @@
 </t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7" t="b">
+      <c r="I7" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21714,7 +21714,7 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Address Number Complete includes the Address Number Prefix (if any), the Address Number, Address Number Suffix (if any), and any formatting or separator characters needed to display the official version of the complete address number. The Address Number Complete precedes the complete street name to identify a location along a thoroughfare or within a defined area.
 Domain: None
@@ -21723,28 +21723,28 @@
 </t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7" t="b">
+      <c r="I8" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
           <t>5.8</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">An identifier that precedes the Address Number and further identifies a location along a thoroughfare or within a defined area.
 Domain: None
@@ -21773,28 +21773,28 @@
 </t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7" t="b">
+      <c r="I9" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21814,7 +21814,7 @@
           <t>5.9</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">An extension of the Address Number that follows it and further identifies a location along a thoroughfare or within a defined area.
 Domain: None
@@ -21823,28 +21823,28 @@
 </t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n">
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="7" t="b">
+      <c r="I10" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21864,7 +21864,7 @@
           <t>5.10</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of a state, province, or territory represented by the two letter UPPERCASE abbreviation given in ISO-3166-2.
 Domain: ISO-3166-2 or USPS Publication 28 (for the United States)
@@ -21873,28 +21873,28 @@
 </t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="n">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="7" t="b">
+      <c r="I11" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -21914,7 +21914,7 @@
           <t>5.11</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Description: The Administrative Level 1 value on the left side of the road segment relative to the FROM Node.
 Domain: ISO-3166-2 or USPS Publication 28 (for the United States)
@@ -21923,28 +21923,28 @@
 </t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="n">
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I12" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="7" t="b">
+      <c r="I12" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -21964,7 +21964,7 @@
           <t>5.12</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 1 value on the right side of the road segment relative to the FROM Node.
 Domain: ISO-3166-2 or USPS Publication 28 (for the United States)
@@ -21973,28 +21973,28 @@
 </t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I13" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="7" t="b">
+      <c r="I13" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
           <t>5.13</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of the primary subdivision of a state, province, or territory.
 Domain: CLDXF-US: A complete list is maintained by the US Census Bureau as ANSI INCITS 31:2009 (Formerly FIPS 6-4) and the Domain is restricted to the exact listed values as published in ANSI INCITS 31:2009, including casing and use of abbreviations.
@@ -22024,28 +22024,28 @@
 </t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7" t="b">
+      <c r="I14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22065,7 +22065,7 @@
           <t>5.14</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 2 value on the left side of the road segment relative to the FROM Node. 
 Domain: CLDXF-US: A complete list is maintained by the US Census Bureau as ANSI INCITS 31:2009 (Formerly FIPS 6-4) and the Domain is restricted to the exact listed values as published in ANSI INCITS 31:2009, including casing and use of abbreviations.
@@ -22075,28 +22075,28 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="n">
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="b">
+      <c r="I15" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22116,7 +22116,7 @@
           <t>5.15</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 2 value on the right side of the road segment relative to the FROM Node.
 Domain: CLDXF-US: A complete list is maintained by the US Census Bureau as ANSI INCITS 31:2009 (Formerly FIPS 6-4) and the Domain is restricted to the exact listed values as published in ANSI INCITS 31:2009, including casing and use of abbreviations.
@@ -22126,28 +22126,28 @@
 </t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7" t="b">
+      <c r="I16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22167,7 +22167,7 @@
           <t>5.16</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of the secondary division of a state, province, or territory. In Canada, where no Administrative Level 2 exists, it can be the name of the primary division of the province or territory.
 Domain: None
@@ -22176,28 +22176,28 @@
 </t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="n">
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="b">
+      <c r="I17" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22217,7 +22217,7 @@
           <t>5.17</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 3 value on the left side of the road segment relative to the FROM Node.
 Domain: None
@@ -22226,28 +22226,28 @@
 </t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="n">
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7" t="b">
+      <c r="I18" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22267,7 +22267,7 @@
           <t>5.18</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 3 value on the right side of the road segment relative to the FROM Node.
 Domain: None
@@ -22276,28 +22276,28 @@
 </t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n">
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" s="7" t="b">
+      <c r="I19" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22317,7 +22317,7 @@
           <t>5.19</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of the subdivision of the most granular preceding administrative level.
 Domain: None
@@ -22326,28 +22326,28 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n">
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="b">
+      <c r="I20" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22367,7 +22367,7 @@
           <t>5.20</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 4 value on the left side of the road segment relative to the FROM Node.
 Domain: None
@@ -22376,28 +22376,28 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="n">
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" s="7" t="b">
+      <c r="I21" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22417,7 +22417,7 @@
           <t>5.21</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 4 value on the right side of the road segment relative to the FROM Node.
 Domain: None
@@ -22426,28 +22426,28 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" s="7" t="b">
+      <c r="I22" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22467,7 +22467,7 @@
           <t>5.22</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of the most granular administrative level supported by this standard. It is typically an unincorporated portion of a preceding administrative level.
 Domain: None
@@ -22476,28 +22476,28 @@
 </t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="n">
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" s="7" t="b">
+      <c r="I23" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
           <t>5.23</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 5 value on the left side of the road segment relative to the FROM Node.
 Domain: None
@@ -22526,28 +22526,28 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="n">
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7" t="b">
+      <c r="I24" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22567,7 +22567,7 @@
           <t>5.24</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Administrative Level 5 value on the right side of the road segment relative to the FROM Node.
 Domain: None
@@ -22576,28 +22576,28 @@
 </t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="n">
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" s="7" t="b">
+      <c r="I25" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22617,7 +22617,7 @@
           <t>5.25</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A Domain Name System (DNS) domain name which is used to uniquely identify an agency. An agency is represented by a fully qualified domain name as defined in NENA-STA-010. In order to correlate actions across a wide range of calls and incidents, each agency MUST use one domain name consistently. Any domain name in the public DNS is acceptable so long as each distinct agency uses a different domain name. This ensures that each agency identifier is globally unique.
 Domain: Fully qualified domain name
@@ -22626,28 +22626,28 @@
 </t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="n">
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I26" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" s="7" t="b">
+      <c r="I26" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -22667,7 +22667,7 @@
           <t>5.26</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A vCard is a file format standard for electronic business cards. The Agency vCard URI is the internet address of a JavaScript Object Notation (JSON) data structure which contains contact information (Name of Agency, Contact phone numbers, etc.) in the form of a jCard (RFC 7095). The vCard URI is used in the service boundary layers to provide contact information for that agency. The Agency Locator (see NENA-STA-010) provides the URIs for Agencies listed in it.
 Domain: None
@@ -22676,28 +22676,28 @@
 </t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="n">
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I27" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" s="7" t="b">
+      <c r="I27" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22717,7 +22717,7 @@
           <t>5.27</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The measure of the orthogonal distance from the WGS84 ellipsoid, given in meters. For Site/Structure Address Points, Altitude measures the orthogonal distance from the WGS84 ellipsoid to the surface (such as a floor or ground).
 Domain: Restricted to a double-precision floating point number with a precision of nine and a scale of three (e.g., REAL (9,3)).
@@ -22726,26 +22726,26 @@
 </t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" s="7" t="b">
+      <c r="I28" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -22765,7 +22765,7 @@
           <t>5.28</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of a country represented by its two letter ISO-3166-1 English country alpha 2 code elements in UPPERCASE letters.
 Domain: Restricted to the two letter designations provided in ISO-3166-1.
@@ -22774,28 +22774,28 @@
 </t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="n">
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I29" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" s="7" t="b">
+      <c r="I29" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -22815,7 +22815,7 @@
           <t>5.29</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of the Country on the left side of the road segment relative to the FROM Node, represented by its two letter ISO-3166-1 English country alpha 2 code elements in UPPERCASE letters.
 Domain: Restricted to the two letter designations provided in ISO-3166-1.
@@ -22824,28 +22824,28 @@
 </t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="n">
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I30" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" s="7" t="b">
+      <c r="I30" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -22865,7 +22865,7 @@
           <t>5.30</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of the Country on the right side of the road segment relative to the FROM Node, represented by its two letter ISO-3166-1 English country alpha 2 code elements in UPPERCASE letters.
 Domain: Restricted to the two letter designations provided in ISO-3166-1.
@@ -22874,28 +22874,28 @@
 </t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="n">
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I31" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J31" s="7" t="b">
+      <c r="I31" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -22915,7 +22915,7 @@
           <t>5.31</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The date and time that the record was created or last modified. This value MUST be populated upon modifications to attributes, geometry, or both.
 Domain: None
@@ -22924,30 +22924,30 @@
 </t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I32" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" s="7" t="b">
+      <c r="I32" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -22967,7 +22967,7 @@
           <t>5.32</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A word that follows all other street name elements and is used only as needed to indicate direction of travel on a divided roadway and associated frontage roads.
 Domain: None
@@ -22976,28 +22976,28 @@
 </t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="n">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I33" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" s="7" t="b">
+      <c r="I33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23017,7 +23017,7 @@
           <t>5.33</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Agency that receives a Discrepancy Report (DR), should a discrepancy be discovered, and will take responsibility for ensuring discrepancy resolution. This may or may not be the same as the 9-1-1 Authority. This MUST be represented by a domain name that is an Agency Identifier as defined in the NENA Knowledge Base Glossary.
 Domain: None
@@ -23025,28 +23025,28 @@
 </t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n">
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I34" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J34" s="7" t="b">
+      <c r="I34" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23066,7 +23066,7 @@
           <t>5.34</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A description or "name" of the service provider that offers services within the area of a Service Boundary. This value MUST be suitable for display.
 Domain: None
@@ -23074,28 +23074,28 @@
 </t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="n">
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I35" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" s="7" t="b">
+      <c r="I35" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23115,7 +23115,7 @@
           <t>5.35</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A physical marker labeled with the distance from or to a given point along a route such as a trail, a waterway, a road, or a highway. 
 Domain: None
@@ -23124,28 +23124,28 @@
 </t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="n">
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>150</v>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" s="7" t="b">
+      <c r="I36" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23165,7 +23165,7 @@
           <t>5.36</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicator of the type of distance marker.
 Domain: P (for Posted); L (for Logical/calculated measurement)
@@ -23173,28 +23173,28 @@
 </t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I37" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" s="7" t="b">
+      <c r="I37" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
           <t>5.37</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The label or text on a physical distance marker. Note that the posted label may be different from the actual measure.
 Domain: None
@@ -23223,28 +23223,28 @@
 </t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="n">
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" s="7" t="b">
+      <c r="I38" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23264,7 +23264,7 @@
           <t>5.38</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Linear distance from a reference point or the actual value of the distance measurement.
 Domain: Restricted to a double-precision floating point number with a precision of nine and a scale of three (e.g., REAL (9,3)).
@@ -23272,26 +23272,26 @@
 </t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="H39" s="7" t="n">
+      <c r="H39" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I39" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J39" s="7" t="b">
+      <c r="I39" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J39" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23311,7 +23311,7 @@
           <t>5.39</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The primary route name the distance marker is associated with.
 Domain: None
@@ -23319,28 +23319,28 @@
 </t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="n">
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I40" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" s="7" t="b">
+      <c r="I40" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23360,7 +23360,7 @@
           <t>5.40</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The type of route the distance marker refers to.
 Domain: None
@@ -23368,28 +23368,28 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="n">
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I41" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" s="7" t="b">
+      <c r="I41" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23409,7 +23409,7 @@
           <t>5.41</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Unit of measurement used for the distance marker.
 Domain: Standardized units of measure
@@ -23417,28 +23417,28 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="n">
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" s="7" t="b">
+      <c r="I42" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -23458,7 +23458,7 @@
           <t>5.42</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The date and time that the record is scheduled to take effect.
 Domain: None
@@ -23468,30 +23468,30 @@
 </t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I43" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" s="7" t="b">
+      <c r="I43" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
           <t>5.43</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The orthogonal distance of the Earth’s surface from the WGS84 ellipsoid given in meters at the Site/Structure Address Point’s latitude and longitude; also, the Altitude of the ground level. Within a structure, this is “the zero floor level.”
 Domain: Restricted to a double-precision floating point number with a precision of nine and a scale of three (e.g., REAL (9,3)).
@@ -23520,26 +23520,26 @@
 </t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" s="7" t="b">
+      <c r="I44" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23559,7 +23559,7 @@
           <t>5.44</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A 3-5 character numeric string that represents one or more Emergency Service Zones (ESZ).
 Domain: Characters from 000 to 99999
@@ -23569,28 +23569,28 @@
 </t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="n">
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" s="7" t="b">
+      <c r="I45" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23610,7 +23610,7 @@
           <t>5.45</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Emergency Service Number (ESN) on the left side of the road segment relative to the FROM Node.
 Domain: Characters from 000 to 99999
@@ -23620,28 +23620,28 @@
 </t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="n">
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" s="7" t="b">
+      <c r="I46" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23661,7 +23661,7 @@
           <t>5.46</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Emergency Service Number (ESN) on the right side of the road segment relative to the FROM Node.
 Domain: Characters from 000 to 99999
@@ -23671,28 +23671,28 @@
 </t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="n">
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I47" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" s="7" t="b">
+      <c r="I47" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23712,7 +23712,7 @@
           <t>5.47</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The date and time when the information in the record is no longer considered valid.
 Domain: None
@@ -23723,30 +23723,30 @@
 </t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>DATETIME</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" s="7" t="b">
+      <c r="I48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23766,7 +23766,7 @@
           <t>5.48</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">An internal counter or index of floor, story, or level within a building stored as an integer to convey the range and relationships between floors. Having a floor integer independent of the floor label provides an absolute measure that can be used to convey and operationalize vertical uncertainty and will assist first responders in arriving at the location of the emergency.
 The level of an addressed main entrance is “0.” Each floor or partial floor is sequentially incremented by 1 above or below 0. This is not intended for user display. It is intended to be used for internal processing or calculations.
@@ -23775,30 +23775,30 @@
 </t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" s="7" t="b">
+      <c r="I49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23818,7 +23818,7 @@
           <t>5.49</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A description of floor, story, or level within a building stored as text. This may be considered part of a “dispatchable location.”
 Domain: None
@@ -23826,28 +23826,28 @@
 </t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="n">
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I50" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" s="7" t="b">
+      <c r="I50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23867,7 +23867,7 @@
           <t>5.50</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Height is the difference between Elevation and Altitude given in meters for a Site/Structure Address Point; often referred to as “Height Above Ground Level” (AGL).
 Domain: Restricted to a double-precision floating point number with a precision of nine and a scale of three (e.g., REAL (9,3)).
@@ -23876,26 +23876,26 @@
 </t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="H51" s="7" t="n">
+      <c r="H51" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" s="7" t="b">
+      <c r="I51" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23915,7 +23915,7 @@
           <t>5.51</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Name of a lake, pond, waterway, or similar body of water.
 Domain: None
@@ -23923,28 +23923,28 @@
 </t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="n">
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I52" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" s="7" t="b">
+      <c r="I52" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -23964,7 +23964,7 @@
           <t>5.52</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Type of water body.
 Domain: None
@@ -23972,28 +23972,28 @@
 </t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="n">
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I53" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J53" s="7" t="b">
+      <c r="I53" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24013,7 +24013,7 @@
           <t>5.53</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of a creek, stream, river, or similar linear water feature.
 Domain: None
@@ -24021,28 +24021,28 @@
 </t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="n">
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I54" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J54" s="7" t="b">
+      <c r="I54" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24062,7 +24062,7 @@
           <t>5.54</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The type of surface water.
 Domain: None
@@ -24070,28 +24070,28 @@
 </t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="n">
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J55" s="7" t="b">
+      <c r="I55" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24111,7 +24111,7 @@
           <t>5.55</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The angular distance of a location north or south of the equator as defined by the coordinate system, expressed in decimal degrees.
 Domain: Restricted to a double-precision floating point number, between +90 degrees to  90 degrees, with a precision of ten and a scale of seven (e.g., REAL (10,7)).
@@ -24119,26 +24119,26 @@
 </t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H56" s="7" t="n">
+      <c r="H56" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I56" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J56" s="7" t="b">
+      <c r="I56" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24158,7 +24158,7 @@
           <t>5.56</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">An identifier that precedes the Address Number, applying to all address numbers on the left side of the road segment relative to the FROM Node, and further identifies a location along a thoroughfare or within a defined area.
 Domain: None
@@ -24167,28 +24167,28 @@
 </t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="n">
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J57" s="7" t="b">
+      <c r="I57" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24208,7 +24208,7 @@
           <t>5.57</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In the RoadCenterLine layer, each feature has a begin point and an endpoint. The FROM Node is the begin point while the TO Node is the endpoint. Each has a left side and a right side relative to a begin node and an end node. The Left FROM address is the address number on the left side of the road segment relative to the FROM Node.
 Domain: None
@@ -24217,30 +24217,30 @@
 </t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I58" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" s="7" t="b">
+      <c r="I58" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24260,7 +24260,7 @@
           <t>5.58</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In the RoadCenterLine layer, each feature has a begin point and an endpoint. The FROM Node is the begin point while the TO Node is the endpoint. Each has a left side and a right side relative to a begin node and an end node. The Left TO address is the address number on the left side of the road segment relative to the TO Node.
 Domain: None
@@ -24269,30 +24269,30 @@
 </t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I59" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" s="7" t="b">
+      <c r="I59" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24312,7 +24312,7 @@
           <t>5.59</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The existing County ID as found in the MSAG for the corresponding MSAG record with which the address point is associated. This is typically the same County ID value found on the corresponding Road Centerline segment.
 Domain: None
@@ -24322,28 +24322,28 @@
 </t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="n">
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G60" s="7" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I60" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J60" s="7" t="b">
+      <c r="I60" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24363,7 +24363,7 @@
           <t>5.60</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The existing County ID as found in the MSAG on the left side of the road segment relative to the FROM Node.
 Domain: None
@@ -24373,28 +24373,28 @@
 </t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="n">
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I61" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" s="7" t="b">
+      <c r="I61" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24414,7 +24414,7 @@
           <t>5.61</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The existing County ID as found in the MSAG on the right side of the road segment relative to the FROM Node.
 Domain: None
@@ -24424,28 +24424,28 @@
 </t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="n">
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I62" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J62" s="7" t="b">
+      <c r="I62" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24465,7 +24465,7 @@
           <t>5.62</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The street name as it currently exists in the MSAG. Ideally, this is the name as assigned by the local addressing authority. However, it is imperative that the content of the “Legacy Street Name” field in the GIS data and the content of the “Street Name” field in the MSAG MUST be identical. If there are discrepancies, one of these two databases (GIS and/or MSAG) MUST be updated to match the other.
 Domain: None
@@ -24475,28 +24475,28 @@
 </t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="n">
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G63" s="7" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I63" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J63" s="7" t="b">
+      <c r="I63" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24516,7 +24516,7 @@
           <t>5.63</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The trailing street direction suffix as it currently exists in the MSAG. Ideally, this is the street name post directional as assigned by the local addressing authority. However, it is imperative that the content of the “Legacy Street Name Post Directional” field in the GIS data and the “Post Directional” field in the MSAG MUST be identical. If there are discrepancies, one of these two databases (GIS and/or MSAG) MUST be updated to match the other.
 Domain: N; S; E; W; NE; NW; SE; SW; O; NO; SO; or equivalent abbreviations in other languages
@@ -24528,28 +24528,28 @@
 </t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="n">
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" s="7" t="b">
+      <c r="I64" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
           <t>5.64</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The leading street direction prefix as it currently exists in the MSAG. Ideally, this is the street name pre directional as assigned by the local addressing authority. However, it is imperative that the “Legacy Street Name Pre Directional” field in the GIS data and the “Prefix Directional” field in the MSAG MUST be identical. If there are discrepancies, one of these two databases (GIS and/or MSAG) MUST be updated to match the other.
 Domain: N; S; E; W; NE; NW; SE; SW; O; NO; SO; or equivalent abbreviations in other languages
@@ -24581,28 +24581,28 @@
 </t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="n">
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H65" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I65" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J65" s="7" t="b">
+      <c r="I65" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -24622,7 +24622,7 @@
           <t>5.65</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The valid street abbreviation as it currently exists in the MSAG. Ideally, this is the street name type as assigned by the local addressing authority. However, it is imperative that the “Legacy Street Name Type” in the GIS data and the “Street Suffix” field in the MSAG MUST be identical. If there are discrepancies, one of these two databases (GIS and/or MSAG) MUST be updated to match the other.
 Domain: None
@@ -24631,28 +24631,28 @@
 </t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="n">
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J66" s="7" t="b">
+      <c r="I66" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24672,7 +24672,7 @@
           <t>5.66</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A uniquely identified and indivisible infrastructure component, smaller than a structure, which exists either within a structure or exterior to any structure, such as an alarm box, a utility pole, a callbox, or other similar features.
 Domain: None
@@ -24681,28 +24681,28 @@
 </t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="n">
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J67" s="7" t="b">
+      <c r="I67" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24722,7 +24722,7 @@
           <t>5.67</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicates whether the location marker is identified by a physical sign.
 Domain: P (for Posted); U (for Unposted)
@@ -24730,28 +24730,28 @@
 </t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H68" s="7" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I68" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" s="7" t="b">
+      <c r="I68" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
           <t>5.68</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The label or text on a physical marker, or if unposted, the description of an unposted marker.
 Domain: None
@@ -24779,28 +24779,28 @@
 </t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="n">
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J69" s="7" t="b">
+      <c r="I69" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24820,7 +24820,7 @@
           <t>5.69</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The type of feature the location marker represents.
 Domain: None
@@ -24828,28 +24828,28 @@
 </t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="n">
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G70" s="7" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" s="7" t="b">
+      <c r="I70" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24869,7 +24869,7 @@
           <t>5.70</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The type of feature the location marker represents.
 Domain: None
@@ -24877,26 +24877,26 @@
 </t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="H71" s="7" t="n">
+      <c r="H71" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71" s="7" t="b">
+      <c r="I71" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24916,7 +24916,7 @@
           <t>5.71</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Community name associated with an address as given in the MSAG and may or may not be the same as the Community Name used by the postal service.
 Domain: None
@@ -24926,28 +24926,28 @@
 </t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="n">
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="G72" s="7" t="inlineStr">
+      <c r="G72" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J72" s="7" t="b">
+      <c r="I72" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -24967,7 +24967,7 @@
           <t>5.72</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The existing MSAG Community Name on the left side of the road segment relative to the FROM Node.
 Domain: None
@@ -24977,28 +24977,28 @@
 </t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="n">
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="G73" s="7" t="inlineStr">
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I73" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" s="7" t="b">
+      <c r="I73" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
           <t>5.73</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The existing MSAG Community Name on the right side of the road segment relative to the FROM Node.
 Domain: None
@@ -25028,28 +25028,28 @@
 </t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="n">
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G74" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I74" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J74" s="7" t="b">
+      <c r="I74" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25069,7 +25069,7 @@
           <t>5.74</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The NENA Globally Unique ID (Primary Key) for each record in a GIS data layer. Each record in the GIS data layer MUST have a globally unique ID. When coalescing data from other local 9-1-1 Authorities into the ECRF and LVF, this unique ID MUST continue to have only one occurrence. Additional details on how to construct the NGUID can be found in Section 3.6 NENA Globally Unique ID (NGUID).
 Domain: None
@@ -25084,28 +25084,28 @@
 </t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="n">
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I75" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" s="7" t="b">
+      <c r="I75" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25125,7 +25125,7 @@
           <t>5.75</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The direction of traffic movement along a road in relation to the FROM node and TO node of the line segment representing the road in the GIS data. The One Way field has three possible designations: B (Both), FT (From–To), and TF (To–From).
 B—Travel in both directions allowed
@@ -25136,28 +25136,28 @@
 </t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="n">
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G76" s="7" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H76" s="7" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I76" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" s="7" t="b">
+      <c r="I76" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25177,7 +25177,7 @@
           <t>5.76</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The even or odd property of the address number range on the left side of the road segment relative to the FROM Node.
 Domain: O=Odd; E=Even; B=Both; Z=Address Range 0 0
@@ -25185,28 +25185,28 @@
 </t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H77" s="7" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I77" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" s="7" t="b">
+      <c r="I77" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25226,7 +25226,7 @@
           <t>5.77</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The even or odd property of the address number range on the right side of the road segment relative to the FROM Node.
 Domain: O=Odd; E=Even; B=Both; Z=Address Range 0 0
@@ -25234,28 +25234,28 @@
 </t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I78" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" s="7" t="b">
+      <c r="I78" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -25275,7 +25275,7 @@
           <t>5.78</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The type of feature identified by the address.
 Domain: CLDXF-US: https://www.iana.org/assignments/location-type-registry/location-type-registry.xml
@@ -25285,28 +25285,28 @@
 </t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="n">
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I79" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" s="7" t="b">
+      <c r="I79" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25326,7 +25326,7 @@
           <t>5.79</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Description: The methodology used for placement of the address point or defining the extent of an address polygon.
 Domain (Address Point): Address point values are restricted to values found in the “NENA Site/Structure Address Point Placement Method Registry” at: http://technet.nena.org/nrs/registry/SiteStructureAddressPointPlacementMethod.xml
@@ -25336,28 +25336,28 @@
 </t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="n">
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G80" s="7" t="inlineStr">
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H80" s="7" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I80" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" s="7" t="b">
+      <c r="I80" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25377,7 +25377,7 @@
           <t>5.80</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A system of codes that identifies an individual Post Office or metropolitan area delivery station associated with an address.
 Domain: As defined by each country’s postal authority (i.e., USPS, Canada Post)
@@ -25386,28 +25386,28 @@
 </t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="n">
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I81" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" s="7" t="b">
+      <c r="I81" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25427,7 +25427,7 @@
           <t>5.81</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A system of 4-digit codes that are used after the US Postal Code to specify a range of USPS delivery addresses.
 Domain: Defined by the USPS
@@ -25436,28 +25436,28 @@
 </t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="n">
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G82" s="7" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H82" s="7" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I82" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J82" s="7" t="b">
+      <c r="I82" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25477,7 +25477,7 @@
           <t>5.82</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Postal Code on the left side of the road segment relative to the FROM Node.
 Domain: As defined by each country’s postal authority (i.e., USPS, Canada Post) 
@@ -25486,28 +25486,28 @@
 </t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="n">
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G83" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I83" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J83" s="7" t="b">
+      <c r="I83" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
           <t>5.86</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The Postal Code on the right side of the road segment relative to the FROM Node.
 Domain: As defined by each country’s postal authority (i.e., USPS, Canada Post) 
@@ -25536,28 +25536,28 @@
 </t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="n">
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G84" s="7" t="inlineStr">
+      <c r="G84" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H84" s="7" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I84" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J84" s="7" t="b">
+      <c r="I84" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
           <t>5.84</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A mailing place name for the Postal Code of an address.
 Domain: CLDXF-US: Restricted to city names given in the USPS City State file for a given Postal Code.
@@ -25587,28 +25587,28 @@
 </t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="n">
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I85" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J85" s="7" t="b">
+      <c r="I85" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
           <t>5.85</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A mailing place name for the Postal Code of an address on the left side of the road segment relative to the FROM Node.
 Domain: CLDXF-US: Restricted to city names given in the USPS City State file for a given Postal code.
@@ -25638,28 +25638,28 @@
 </t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="n">
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="G86" s="7" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H86" s="7" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I86" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" s="7" t="b">
+      <c r="I86" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25679,7 +25679,7 @@
           <t>5.86</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A mailing place name for the Postal Code of an address on the right side of the road segment relative to the FROM Node.
 Domain: CLDXF-US: Restricted to city names given in the USPS City State file for a given Postal code.
@@ -25689,28 +25689,28 @@
 </t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="n">
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I87" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J87" s="7" t="b">
+      <c r="I87" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
           <t>5.87</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The word or phrase that constitutes the distinctive designation of the rail line.
 Domain: None
@@ -25738,28 +25738,28 @@
 </t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="n">
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G88" s="7" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H88" s="7" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I88" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J88" s="7" t="b">
+      <c r="I88" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25779,7 +25779,7 @@
           <t>5.88</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of the operator of the rail line or the primary rail company with rights to use the rail line.
 Domain: None
@@ -25787,28 +25787,28 @@
 </t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="n">
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="G89" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H89" s="7" t="inlineStr">
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I89" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J89" s="7" t="b">
+      <c r="I89" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25828,7 +25828,7 @@
           <t>5.89</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of the owner of the rail right of way.
 Domain: None
@@ -25836,28 +25836,28 @@
 </t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="n">
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G90" s="7" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H90" s="7" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I90" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J90" s="7" t="b">
+      <c r="I90" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25877,7 +25877,7 @@
           <t>5.90</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The ending linear reference of the named rail line.
 Domain: Restricted to a double-precision floating point number with a precision of seven and a scale of three (e.g., REAL (7,3)).
@@ -25885,26 +25885,26 @@
 </t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n">
+      <c r="G91" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H91" s="7" t="n">
+      <c r="H91" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I91" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J91" s="7" t="b">
+      <c r="I91" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
           <t>5.91</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The beginning linear reference of the named rail line.
 Domain: Restricted to a double-precision floating point number with a precision of seven and a scale of three (e.g., REAL (7,3)).
@@ -25932,26 +25932,26 @@
 </t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
+      <c r="G92" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="H92" s="7" t="n">
+      <c r="H92" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I92" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J92" s="7" t="b">
+      <c r="I92" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -25971,7 +25971,7 @@
           <t>5.92</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">An identifier that precedes the Address Number, applying to all address numbers on the right side of the road segment relative to the FROM Node, and further identifies a location along a thoroughfare or within a defined area.
 Domain: None
@@ -25980,28 +25980,28 @@
 </t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="n">
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I93" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J93" s="7" t="b">
+      <c r="I93" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26021,7 +26021,7 @@
           <t>5.93</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In the RoadCenterLine layer, each feature has a begin point and an endpoint. The FROM Node is the begin point while the TO node is the endpoint. Each has a left side and a right side relative to a begin node and an end node. The Right FROM address number is the address number on the right side of the road segment relative to the FROM Node.
 Domain: None
@@ -26030,30 +26030,30 @@
 </t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr">
+      <c r="G94" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H94" s="7" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I94" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J94" s="7" t="b">
+      <c r="I94" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26073,7 +26073,7 @@
           <t>5.94</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">In the RoadCenterLine layer, each feature has a begin point and an endpoint. The FROM Node is the begin point while the TO node is the endpoint. Each has a left side and a right side relative to a begin node and an end node. The Right TO address number is the address number on the right side of the road segment relative to the TO Node.
 Domain: None
@@ -26082,30 +26082,30 @@
 </t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr">
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I95" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J95" s="7" t="b">
+      <c r="I95" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
           <t>5.95</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The general description of the type of road. The Road Classifications used in this document are derived from the US Census MAF/TIGER Feature Classification Codes (MTFCC), which is an update to the now deprecated Census Feature Class Codes (CFCC).
 Domain: Primary; Secondary; Local; Ramp; Service Drive; Vehicular Trail; Walkway/Pedestrian Trail; Stairway; Alley; Private; Parking Lot; Bike Path or Trail; Bridle Path; Other
@@ -26148,28 +26148,28 @@
 </t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="n">
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="G96" s="7" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I96" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J96" s="7" t="b">
+      <c r="I96" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -26189,7 +26189,7 @@
           <t>5.96</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A single, distinctly identified, enclosed space within a structure.
 Domain: None
@@ -26198,28 +26198,28 @@
 </t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="n">
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I97" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J97" s="7" t="b">
+      <c r="I97" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J97" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26239,7 +26239,7 @@
           <t>5.97</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">An identified linear feature, such as a linear arrangement of seats, workstations, equipment, or storage, within a structure, wing, unit, room, or section.
 Domain: None
@@ -26248,28 +26248,28 @@
 </t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="n">
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G98" s="7" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I98" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J98" s="7" t="b">
+      <c r="I98" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J98" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26289,7 +26289,7 @@
           <t>5.98</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">An identified seat, desk, workstation, cubicle, or similar precise location within a structure, wing, unit, room, section, or row.
 Domain: None
@@ -26298,28 +26298,28 @@
 </t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="n">
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G99" s="7" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H99" s="7" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I99" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J99" s="7" t="b">
+      <c r="I99" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J99" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26339,7 +26339,7 @@
           <t>5.99</t>
         </is>
       </c>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">An identified, unenclosed area within a structure, wing, unit, or room.
 Domain: None
@@ -26348,28 +26348,28 @@
 </t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="n">
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I100" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J100" s="7" t="b">
+      <c r="I100" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J100" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26389,7 +26389,7 @@
           <t>5.100</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The numbers that would be dialed on a 12 digit keypad to reach the service appropriate for the location. This is not the same as an Emergency Service Number (ESN) in Legacy E9-1-1 systems. This field is used for all service boundary layers including PsapPolygon, PolicePolygon, FirePolygon, EmsPolygon, and others such as PoisonControlPolygon. Within North America, the Service Number for most services is 9-1-1; however, there may be service boundaries that have a different number that may be associated with them such as Poison Control. Additionally, in some countries, different numbers may be used for Police, Fire, and EMS—this field would be used to denote those numbers.
 Domain: A dialable number or dial string
@@ -26397,28 +26397,28 @@
 </t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="n">
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G101" s="7" t="inlineStr">
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H101" s="7" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I101" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J101" s="7" t="b">
+      <c r="I101" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J101" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26438,7 +26438,7 @@
           <t>5.101</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">URI for call routing. This attribute is contained in the service boundary layers and will define the URI of the service. The URI is usually a Session Initiation Protocol (e.g., SIP or SIPs) URI that defines the initial route or path the call will take towards the PSAP or agency represented by the boundary.
 Domain: Registered domain name
@@ -26450,28 +26450,28 @@
 </t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="n">
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F102" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G102" s="7" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I102" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J102" s="7" t="b">
+      <c r="I102" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -26491,7 +26491,7 @@
           <t>5.102</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The URN used to select the service for which a route is desired. The ECRF is queried with a location and a Service URN that returns the URI of the appropriate service.
 Domain: RFC 5031 defines the Service URN; NENA-STA-010 defines the domain of allowable values. PSAP boundaries SHOULD only contain features with Service URN values of "urn:emergency:service:sos.psap." Values to be used for service boundaries for other responding agencies are found in the IANA urn:emergency:service:responder registry.
@@ -26502,28 +26502,28 @@
 </t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="n">
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="G103" s="7" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H103" s="7" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I103" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J103" s="7" t="b">
+      <c r="I103" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -26543,7 +26543,7 @@
           <t>5.103</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of an exterior area that is publicly known and unique within a given place. A site may contain one or more structures and/or subsites. 
 Domain: None
@@ -26552,28 +26552,28 @@
 </t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="n">
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F104" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G104" s="7" t="inlineStr">
+      <c r="G104" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H104" s="7" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I104" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J104" s="7" t="b">
+      <c r="I104" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J104" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26593,7 +26593,7 @@
           <t>5.104</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Posted Speed Limit in MPH or Km/h.
 Domain: Whole numbers from 1 to 999
@@ -26601,30 +26601,30 @@
 </t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H105" s="7" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I105" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J105" s="7" t="b">
+      <c r="I105" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J105" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -26644,7 +26644,7 @@
           <t>5.105</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The element of the complete street name that identifies the particular thoroughfare (as opposed to any street types, directionals, and modifiers).
 Domain: None
@@ -26653,28 +26653,28 @@
 </t>
         </is>
       </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="n">
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G106" s="7" t="inlineStr">
+      <c r="G106" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H106" s="7" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I106" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J106" s="7" t="b">
+      <c r="I106" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J106" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26694,7 +26694,7 @@
           <t>5.106</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D107" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A word following the Street Name element that indicates the direction taken by the thoroughfare from an arbitrary starting point or line, or the sector where it is located.
 Domain: North; South; East; West; Northeast; Northwest; Southeast; Southwest; Nord; Sud; Est; Ouest; Nord Est; Nord Ouest; Sud Est; Sud Ouest; or equivalent words in other languages
@@ -26703,28 +26703,28 @@
 </t>
         </is>
       </c>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="n">
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H107" s="7" t="inlineStr">
+      <c r="H107" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I107" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J107" s="7" t="b">
+      <c r="I107" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J107" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -26744,7 +26744,7 @@
           <t>5.107</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr">
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A word or phrase that follows and modifies the Street Name element but is separated from it by a Street Name Post Type or a Street Name Post Directional or both.
 Domain: None
@@ -26753,28 +26753,28 @@
 </t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="n">
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F108" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G108" s="7" t="inlineStr">
+      <c r="G108" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H108" s="7" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I108" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J108" s="7" t="b">
+      <c r="I108" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J108" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26794,7 +26794,7 @@
           <t>5.108</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A word or phrase that follows the Street Name element and identifies a type of thoroughfare in a complete street name.
 Domain: Restricted to values found in the “NENA Registry of Street Name Pre Types and Street Name Post Types” or combinations thereof at:
@@ -26804,28 +26804,28 @@
 </t>
         </is>
       </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="n">
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G109" s="7" t="inlineStr">
+      <c r="G109" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H109" s="7" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I109" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J109" s="7" t="b">
+      <c r="I109" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J109" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -26845,7 +26845,7 @@
           <t>5.109</t>
         </is>
       </c>
-      <c r="D110" s="8" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A word preceding the Street Name element that indicates the direction taken by the thoroughfare from an arbitrary starting point or line, or the sector where it is located.
 Domain: North; South; East; West; Northeast; Northwest; Southeast; Southwest; Nord; Sud; Est; Ouest; Nord Est; Nord Ouest; Sud Est; Sud Ouest; or equivalent words in other languages
@@ -26854,28 +26854,28 @@
 </t>
         </is>
       </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="n">
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G110" s="7" t="inlineStr">
+      <c r="G110" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H110" s="7" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I110" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J110" s="7" t="b">
+      <c r="I110" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J110" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -26895,7 +26895,7 @@
           <t>5.110</t>
         </is>
       </c>
-      <c r="D111" s="8" t="inlineStr">
+      <c r="D111" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A word or phrase that precedes and modifies the Street Name element but is separated from it by a Street Name Pre Type or a Street Name Pre Directional or both.
 Domain: None
@@ -26904,28 +26904,28 @@
 </t>
         </is>
       </c>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="n">
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G111" s="7" t="inlineStr">
+      <c r="G111" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H111" s="7" t="inlineStr">
+      <c r="H111" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I111" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J111" s="7" t="b">
+      <c r="I111" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J111" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
           <t>5.111</t>
         </is>
       </c>
-      <c r="D112" s="8" t="inlineStr">
+      <c r="D112" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A word or phrase that precedes the Street Name element and identifies a type of thoroughfare in a complete street name.
 Domain: Restricted to values found in the “NENA Registry of Street Name Pre Types and Street Name Post Types” or combinations thereof at: http://technet.nena.org/nrs/registry/StreetNamePreTypesAndStreetNamePostTypes.xml
@@ -26954,28 +26954,28 @@
 </t>
         </is>
       </c>
-      <c r="E112" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F112" s="7" t="n">
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G112" s="7" t="inlineStr">
+      <c r="G112" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H112" s="7" t="inlineStr">
+      <c r="H112" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I112" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J112" s="7" t="b">
+      <c r="I112" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J112" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -26995,7 +26995,7 @@
           <t>5.112</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A preposition or prepositional phrase between the Street Name Pre Type and the Street Name.
 Domain: Restricted to values found in the “NENA Registry of Street Name Pre
@@ -27005,28 +27005,28 @@
 </t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="n">
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="G113" s="7" t="inlineStr">
+      <c r="G113" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H113" s="7" t="inlineStr">
+      <c r="H113" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I113" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J113" s="7" t="b">
+      <c r="I113" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J113" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -27046,7 +27046,7 @@
           <t>5.113</t>
         </is>
       </c>
-      <c r="D114" s="8" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A built feature with a vertical dimension, including both conventional buildings with walls, doors, and a roof, and other kinds of infrastructure such as cell towers, transformer stations, and fuel tanks.
 Domain: None
@@ -27055,28 +27055,28 @@
 </t>
         </is>
       </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="n">
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G114" s="7" t="inlineStr">
+      <c r="G114" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H114" s="7" t="inlineStr">
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I114" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J114" s="7" t="b">
+      <c r="I114" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J114" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27096,7 +27096,7 @@
           <t>5.114</t>
         </is>
       </c>
-      <c r="D115" s="8" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">The name of a sub-area within a larger area specified either by a site name, a thoroughfare address, or both.
 Domain: None
@@ -27105,28 +27105,28 @@
 </t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="n">
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="G115" s="7" t="inlineStr">
+      <c r="G115" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H115" s="7" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I115" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J115" s="7" t="b">
+      <c r="I115" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J115" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27146,7 +27146,7 @@
           <t>5.115</t>
         </is>
       </c>
-      <c r="D116" s="8" t="inlineStr">
+      <c r="D116" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A group or suite of rooms within a building, under common ownership or tenancy, typically having a common primary entrance.
 Domain: None
@@ -27155,28 +27155,28 @@
 </t>
         </is>
       </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="n">
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G116" s="7" t="inlineStr">
+      <c r="G116" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H116" s="7" t="inlineStr">
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I116" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J116" s="7" t="b">
+      <c r="I116" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J116" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27196,7 +27196,7 @@
           <t>5.116</t>
         </is>
       </c>
-      <c r="D117" s="8" t="inlineStr">
+      <c r="D117" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Part of the complete unit identifier that precedes the Unit Value and indicates the kind of unit.
 Domain: None
@@ -27205,28 +27205,28 @@
 </t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="n">
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G117" s="7" t="inlineStr">
+      <c r="G117" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H117" s="7" t="inlineStr">
+      <c r="H117" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I117" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J117" s="7" t="b">
+      <c r="I117" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J117" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27246,7 +27246,7 @@
           <t>5.117</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Part of the complete unit identifier that uniquely identifies a particular unit.
 Domain: None
@@ -27255,28 +27255,28 @@
 </t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="n">
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F118" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G118" s="7" t="inlineStr">
+      <c r="G118" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H118" s="7" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I118" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J118" s="7" t="b">
+      <c r="I118" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J118" s="8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -27296,7 +27296,7 @@
           <t>5.118</t>
         </is>
       </c>
-      <c r="D119" s="8" t="inlineStr">
+      <c r="D119" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicates if the address range on the left side of the road segment, relative to the FROM node, should be used for civic location validation. A value of “Y” MAY be entered if any Address Number within the address range on the left side of the road segment should be considered by the LVF to be valid. A value of “N” MAY be entered if the Address Number should only be validated using the SiteStructureAddressPoint layer. If not present, a value of “Y” is assumed.
 Domain: Y; N
@@ -27304,28 +27304,28 @@
 </t>
         </is>
       </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F119" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="7" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H119" s="7" t="inlineStr">
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I119" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J119" s="7" t="b">
+      <c r="I119" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J119" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -27345,7 +27345,7 @@
           <t>5.119</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicates if the address range on the right side of the road segment, relative to the FROM node, should be used for civic location validation. A value of “Y” MAY be entered if any Address Number within the address range on the right side of the road segment should be considered by the LVF to be valid. A value of “N” MAY be entered if the Address Number should only be validated using the SiteStructureAddressPoint layer. If not present, a value of “Y” is assumed.
 Domain: Y; N
@@ -27353,28 +27353,28 @@
 </t>
         </is>
       </c>
-      <c r="E120" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="7" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H120" s="7" t="inlineStr">
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I120" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J120" s="7" t="b">
+      <c r="I120" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J120" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -27394,7 +27394,7 @@
           <t>5.120</t>
         </is>
       </c>
-      <c r="D121" s="8" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">A designated part of a structure that spans one or more floors, typically including more than one unit or room and representing a significant portion of the structure’s floor area.
 Domain: None
@@ -27403,28 +27403,28 @@
 </t>
         </is>
       </c>
-      <c r="E121" s="7" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="F121" s="7" t="n">
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="G121" s="7" t="inlineStr">
+      <c r="G121" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="H121" s="7" t="inlineStr">
+      <c r="H121" s="8" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="I121" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J121" s="7" t="b">
+      <c r="I121" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J121" s="8" t="b">
         <v>0</v>
       </c>
     </row>

--- a/flatfile_templates/prebuilt_templates/v3.0/NG911_GISDataModelSchemaReport_v3.0.xlsx
+++ b/flatfile_templates/prebuilt_templates/v3.0/NG911_GISDataModelSchemaReport_v3.0.xlsx
@@ -20538,7 +20538,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roads data is maintained as a line layer for representing the centerline of a roadway. This dataset is referred to as the RoadCenterLine layer in the GIS Data Layers and Indicators registry in Section 7.1 “GIS Data Layers” Registry “GIS Layers and Indicators” Registry and in NENA documents going forward. GIS road centerline arc node topology is associated with attribute data containing information on street names, address ranges, jurisdictional boundaries, and other attributes. The RoadCenterLine layer is an integral part of any public safety GIS due to its versatility and use for:
+          <t xml:space="preserve">Roads data is maintained as a line layer for representing the centerline of a roadway. This dataset is referred to as the RoadCenterLine layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward. GIS road centerline arc node topology is associated with attribute data containing information on street names, address ranges, jurisdictional boundaries, and other attributes. The RoadCenterLine layer is an integral part of any public safety GIS due to its versatility and use for:
 •	Querying and geocoding of civic addresses based on dual (left/right) address ranges
 •	Tactical map display
 •	Map and attribute viewing
@@ -20587,7 +20587,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Site/Structure Addresses data is maintained as a point layer that supports 3D for representing the location of a site, a structure, an interior space, or access to a site, structure, or an interior space. This dataset is referred to as the SiteStructureAddressPoint layer in in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.  While the SiteStructureAddressPoint layer is required, there is no requirement for the completeness of these data. It is understood that it will take time and resources to develop complete and accurate Site/Structure Addresses data.
+          <t xml:space="preserve">Site/Structure Addresses data is maintained as a point layer that supports 3D for representing the location of a site, a structure, an interior space, or access to a site, structure, or an interior space. This dataset is referred to as the SiteStructureAddressPoint layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward. While the SiteStructureAddressPoint layer is required, there is no requirement for the completeness of these data. It is understood that it will take time and resources to develop complete and accurate Site/Structure Addresses data.
 Site/Structure Addresses data can be used to locate sites that otherwise may not geocode correctly using the road centerline data. It can also be used to locate areas of unusual addressing (i.e., odd addresses on the even side of the road centerlines and vice versa), and other areas where the data is available. Some addressable locations may be problematic near boundaries.
 The Address Number, Street Name, and Administrative Levels 1-5 attributes in the SiteStructureAddressPoint layer SHOULD be consistent with the address number range, street name, and left/right Administrative Level attribute combinations found in the RoadCenterLine layer.
 While there may be address data available, it may not be in the standardized format of this structure. GIS Data Providers should be working toward developing and maintaining the Site/Structure Addresses data described in this Standard.
@@ -20631,9 +20631,9 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Site/Structure Addresses data is maintained as a polygon layer to represent the extent of addressable areas such as outdoor sites, structures, or interior spaces. This dataset is referred to as the SiteStructureAddressPolygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. It is understood that it will take time and resources to fully develop complete and accurate Site/Structure Addresses data.
+          <t xml:space="preserve">Site/Structure Addresses data is maintained as a polygon layer to represent the extent of addressable areas such as outdoor sites, structures, or interior spaces. This dataset is referred to as the SiteStructureAddressPolygon layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward. It is understood that it will take time and resources to fully develop complete and accurate Site/Structure Addresses data.
 Site/Structure Address Polygon data can be used to more effectively convert geodetic locations into civic locations than Site/Structure Address Point data. This is because the polygon represents the extent of the space whereas the point provides no information as to its extent. Gaps and overlaps between SiteStructureAddressPolygon features MAY exist and are permissible (e.g., a room on a floor within a building may be represented as three overlapping SiteStructureAddressPolygon features).
-The SiteStructureAddressPolygon feature attribution SHOULD be consistent with the attribution of related SiteStructureAddressPoint or RoadCenterLine features where they exist.
+SiteStructureAddressPolygon feature attribution SHOULD be consistent with the attribution of related SiteStructureAddressPoint or RoadCenterLine features where they exist.
 While there may be address data available, it may not be in the standardized format of this structure. GIS Data Providers should be working toward developing and maintaining the Site/Structure Address Polygon data described in this Standard.
 </t>
         </is>
@@ -20722,7 +20722,7 @@
 •	Police
 •	Fire
 •	Emergency Medical Services
-Each of these layers is used by the ECRF to perform a geographic query to determine which agencies are responsible for providing service to a location in the event a selective transfer is desired, or to direct an EIDO to an agency for dispatch, or to display the responsible agencies at the PSAP. In addition, service boundary layers are used by PSAPs to identify the appropriate entities/first responders to be dispatched. Each layer representing a primary emergency service may contain one or more polygon boundaries that define the primary emergency services for that geographic area.
+Each of these layers is used by the ECRF to perform a geographic query to determine which agencies are responsible for providing service to a location in the event a selective transfer is desired or to direct an EIDO to an agency for dispatch or to display the responsible agencies at the PSAP. In addition, service boundary layers are used by PSAPs to identify the appropriate entities/first responders to be dispatched. Each layer representing a primary emergency service may contain one or more polygon boundaries that define the primary emergency services for that geographic area.
 *Note: The service boundary layers described here are intended to represent the entirety of the service boundary of the agencies. In many agencies, the service boundary is broken into smaller areas served by a station/beat/platoon, with the service area of the agency being the union of the smaller areas. The layer can contain a polygon set (more than one polygon), which is intended to cover holes, and disconnected areas of service, which does occur. Because a polygon set is allowed, if this layer had the smaller polygons and if all of them have the same Service URI and Service URN (but not necessarily the same Display Name, for example), it would work correctly. It has the downside of increasing work on the ECRF since it has more polygons to consider. The SI Operator can advise whether small polygons can be accommodated in any given implementation.
 </t>
         </is>
@@ -20769,7 +20769,7 @@
 •	Police
 •	Fire
 •	Emergency Medical Services
-Each of these layers is used by the ECRF to perform a geographic query to determine which agencies are responsible for providing service to a location in the event a selective transfer is desired, or to direct an EIDO to an agency for dispatch, or to display the responsible agencies at the PSAP. In addition, service boundary layers are used by PSAPs to identify the appropriate entities/first responders to be dispatched. Each layer representing a primary emergency service may contain one or more polygon boundaries that define the primary emergency services for that geographic area.
+Each of these layers is used by the ECRF to perform a geographic query to determine which agencies are responsible for providing service to a location in the event a selective transfer is desired or to direct an EIDO to an agency for dispatch or to display the responsible agencies at the PSAP. In addition, service boundary layers are used by PSAPs to identify the appropriate entities/first responders to be dispatched. Each layer representing a primary emergency service may contain one or more polygon boundaries that define the primary emergency services for that geographic area.
 *Note: The service boundary layers described here are intended to represent the entirety of the service boundary of the agencies. In many agencies, the service boundary is broken into smaller areas served by a station/beat/platoon, with the service area of the agency being the union of the smaller areas. The layer can contain a polygon set (more than one polygon), which is intended to cover holes, and disconnected areas of service, which does occur. Because a polygon set is allowed, if this layer had the smaller polygons and if all of them have the same Service URI and Service URN (but not necessarily the same Display Name, for example), it would work correctly. It has the downside of increasing work on the ECRF since it has more polygons to consider. The SI Operator can advise whether small polygons can be accommodated in any given implementation.
 </t>
         </is>
@@ -20816,7 +20816,7 @@
 •	Police
 •	Fire
 •	Emergency Medical Services
-Each of these layers is used by the ECRF to perform a geographic query to determine which agencies are responsible for providing service to a location in the event a selective transfer is desired, or to direct an EIDO to an agency for dispatch, or to display the responsible agencies at the PSAP. In addition, service boundary layers are used by PSAPs to identify the appropriate entities/first responders to be dispatched. Each layer representing a primary emergency service may contain one or more polygon boundaries that define the primary emergency services for that geographic area.
+Each of these layers is used by the ECRF to perform a geographic query to determine which agencies are responsible for providing service to a location in the event a selective transfer is desired or to direct an EIDO to an agency for dispatch or to display the responsible agencies at the PSAP. In addition, service boundary layers are used by PSAPs to identify the appropriate entities/first responders to be dispatched. Each layer representing a primary emergency service may contain one or more polygon boundaries that define the primary emergency services for that geographic area.
 *Note: The service boundary layers described here are intended to represent the entirety of the service boundary of the agencies. In many agencies, the service boundary is broken into smaller areas served by a station/beat/platoon, with the service area of the agency being the union of the smaller areas. The layer can contain a polygon set (more than one polygon), which is intended to cover holes, and disconnected areas of service, which does occur. Because a polygon set is allowed, if this layer had the smaller polygons and if all of them have the same Service URI and Service URN (but not necessarily the same Display Name, for example), it would work correctly. It has the downside of increasing work on the ECRF since it has more polygons to consider. The SI Operator can advise whether small polygons can be accommodated in any given implementation.
 </t>
         </is>
@@ -20860,10 +20860,10 @@
         <is>
           <t xml:space="preserve">In an NG9-1-1 deployment, the transfer of 9-1-1 calls uses service boundary layers, all with the same data structure. These agencies may be served by a call center, dispatch center, or other terms.
 Other service boundary layers, which may be maintained as separate or combined, MAY include, but are not limited to:
-  •	Poison Control
-  •	Forest Service
-  •	Coast Guard
-  •	Animal Control
+•	Poison Control
+•	Forest Service
+•	Coast Guard
+•	Animal Control
 </t>
         </is>
       </c>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provisioning Boundaries data is maintained as a polygon layer for representing the area of GIS data provisioning responsibility, with no unintentional gaps or overlaps. This dataset is commonly referred to as the ProvisioningPolygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. The Provisioning Boundary MUST align with data from all adjoining GIS Data Providers.
+          <t xml:space="preserve">Provisioning Boundaries data is maintained as a polygon layer for representing the area of GIS data provisioning responsibility, with no unintentional gaps or overlaps. This dataset is commonly referred to as the ProvisioningPolygon layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward. The Provisioning Boundary MUST align with data from all adjoining GIS Data Providers.
 A Provisioning Boundary can take on a variety of shapes; for example, it may represent the extent of a city, the extent of a county, a region with multiple cities and counties, or possibly the extent of all areas served by a particular PSAP.
 When provisioning data for an ECRF and LVF through the SI, a GIS Data Provider MUST only include GIS data within their Provisioning Boundary and MUST ensure the data includes coverage for the entire extent of their Provisioning Boundary. The Spatial Interface Operator will utilize the ProvisioningPolygon layer to ensure that these requirements are met.
 Note: The 9-1-1 Authority is ultimately responsible for the GIS data within the area they provide service for.
@@ -20946,7 +20946,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrative Level 1 data, formerly States or Equivalents (A1) data, is maintained as a polygon layer for representing the geographic area of a state, province, territory, or other top level subdivision of the larger country corresponding to the PIDF LO A1 element. This dataset is referred to as the A1Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
+          <t xml:space="preserve">Administrative Level 1 data, formerly States or Equivalents (A1) data, is maintained as a polygon layer for representing the geographic area of a state, province, territory, or other top level subdivision of the larger country corresponding to the PIDF-LO A1 element. This dataset is referred to as the A1Polygon layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward.
 </t>
         </is>
       </c>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrative Level 2 data, formerly Counties or Equivalents (A2) data, is maintained as a polygon layer. It typically represents the geographic area of a county, parish, regional district, or other similar level division corresponding to the PIDF LO A2 element. The presence of A2 polygon records is conditional based on the CLDXF Standard applicable to their country. This dataset is referred to as the A2Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
+          <t xml:space="preserve">Administrative Level 2 data, formerly Counties or Equivalents (A2) data, is maintained as a polygon layer. It typically represents the geographic area of a county, parish, regional district, or other similar level division corresponding to the PIDF-LO A2 element. The presence of A2 polygon records is conditional based on the CLDXF Standard applicable to the country of the GIS Data Provider. This dataset is referred to as the A2Polygon layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward.
 </t>
         </is>
       </c>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrative Level 3 data, formerly Incorporated Municipalities (A3) data, is maintained as a polygon layer. It typically represents the geographic area of a city, town, village, or other similar level division corresponding to the PIDF LO A3 element. The presence of A3 polygon records is conditional based on the CLDXF Standard applicable to their country. This dataset is referred to as the A3Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
+          <t xml:space="preserve">Administrative Level 3 data, formerly Incorporated Municipalities (A3) data, is maintained as a polygon layer. It typically represents the geographic area of a city, town, village, or other similar level division corresponding to the PIDF-LO A3 element. The presence of A3 polygon records is conditional based on the CLDXF Standard applicable to the country of the GIS Data Provider. This dataset is referred to as the A3Polygon layer in the GIS Layers and Indicators registry in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward.
 </t>
         </is>
       </c>
@@ -21069,7 +21069,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrative Level 4 data, formerly Unincorporated Communities (A4) data, is maintained as a polygon layer. It typically represents the geographic area of an unincorporated community, borough, ward, or other similar level division corresponding to the PIDF LO A4 element. The presence of A4 polygon records is conditional based on the CLDXF Standard applicable to their country. This dataset is referred to as the A4Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
+          <t xml:space="preserve">Administrative Level 4 data, formerly Unincorporated Communities (A4) data, is maintained as a polygon layer. It typically represents the geographic area of an unincorporated community, borough, ward, or other similar level division corresponding to the PIDF-LO A4 element. The presence of A4 polygon records is conditional based on the CLDXF Standard applicable to the country of the GIS Data Provider. This dataset is referred to as the A4Polygon layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward.
 </t>
         </is>
       </c>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrative Level 5 data, formerly Neighborhood Communities (A5) data, is maintained as a polygon layer. It typically represents the geographic area of a neighborhood, commercial area, or other similar level division corresponding to the PIDF LO A5 element. The presence of A5 polygon records is conditional based on the CLDXF Standard applicable to their country. This dataset is referred to as the A5Polygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
+          <t xml:space="preserve">Administrative Level 5 data, formerly Neighborhood Communities (A5) data, is maintained as a polygon layer. It typically represents the geographic area of a neighborhood, commercial area, or other similar level division corresponding to the PIDF-LO A5 element. The presence of A5 polygon records is conditional based on the CLDXF Standard applicable to the country of the GIS Data Provider. This dataset is referred to as the A5Polygon layer in the GIS Layers and Indicators registry in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward.
 </t>
         </is>
       </c>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Railroads data is maintained as a line layer for representing the centerline of a real world rail line. This dataset is referred to as the RailroadCenterLine layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Federal Railroad Administration’s Rail Lines database is in Appendix A of NENA-STA-006. A database structure crosswalk between this model and Canada’s National Railway Network database is in Appendix B of NENA-STA-006.
+          <t xml:space="preserve">Railroads data is maintained as a line layer for representing the centerline of a rail line. This dataset is referred to as the RailroadCenterLine layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Federal Railroad Administration’s Rail Lines database is in Appendix A—United States’ Federal Railroad Association (FRA) Rail Lines Database Structure Crosswalk to NENA’s RailroadCenterLine Layer of this document. A database structure crosswalk between this model and Canada’s National Railway Network database is in Appendix B—Canada’s National Railway Network Database Structure Crosswalk to NENA’s RailroadCenterLine Layer of this document.
 </t>
         </is>
       </c>
@@ -21190,7 +21190,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hydrology data is maintained as a line layer for representing creeks, streams, rivers, and other linear water features. This dataset is referred to as the HydrologyLine layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Geological Survey’s National Hydrography Dataset (NHD) database is in Appendix C of NENA-STA-006. A database structure crosswalk between this model and Canada’s National Hydrographic Network database is in Appendix D of NENA-STA-006.
+          <t xml:space="preserve">Hydrology data is maintained as a line layer for representing creeks, streams, rivers, and other linear water features. This dataset is referred to as the HydrologyLine layer in the GIS Layers and Indicators registry in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Geological Survey’s National Hydrography Dataset (NHD) database is in Appendix C—United States’ National Hydrography Dataset (NHD) Database Structure Crosswalk to NENA’s HydrologyLine Layer and HydrologyPolygon Layer of this document. A database structure crosswalk between this model and Canada’s National Hydrographic Network database is in Appendix D—Canada’s National Hydrographic Network Database Structure Crosswalk to NENA’s HydrologyLine Layer and HydrologyPolygon Layer of this document.
 </t>
         </is>
       </c>
@@ -21231,7 +21231,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hydrology data is maintained as a polygon layer for representing areal water body features. This dataset is referred to as the HydrologyPolygon layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Geological Survey’s National Hydrography Dataset (NHD) database is in Appendix C of NENA-STA-006. A database structure crosswalk between this model and Canada’s National Hydrographic Network database is in Appendix D of NENA-STA-006.
+          <t xml:space="preserve">Hydrology data is maintained as a polygon layer for representing the area of water features. This dataset is referred to as the HydrologyPolygon layer in the GIS Layers and Indicators registry in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward. A database structure crosswalk between this model and the United States Geological Survey’s National Hydrography Dataset (NHD) database is in Appendix C—United States’ National Hydrography Dataset (NHD) Database Structure Crosswalk to NENA’s HydrologyLine Layer and HydrologyPolygon Layer of this document. A database structure crosswalk between this model and Canada’s National Hydrographic Network database is in Appendix D—Canada’s National Hydrographic Network Database Structure Crosswalk to NENA’s HydrologyLine Layer and HydrologyPolygon Layer of this document.
 </t>
         </is>
       </c>
@@ -21270,7 +21270,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distance Markers data is maintained as a point layer and is used primarily for map display purposes. If required for ECRF and LVF purposes, Distance Markers data MUST be included in the SiteStructureAddressPoint layer. Distance Markers may represent a numeric measurement of a point along a route, such as a mile marker. This dataset is referred to as the DistanceMarkerPoint layer in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
+          <t xml:space="preserve">Distance Markers data is maintained as a point layer and is used primarily for map display purposes. If required for ECRF and LVF purposes, Distance Markers data MUST be included in the SiteStructureAddressPoint layer. Distance Markers may represent a numeric measurement of a point along a route, such as a mile marker. This dataset is referred to as the DistanceMarkerPoint layer in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward.
 </t>
         </is>
       </c>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Location Markers data is maintained as a point layer and is used primarily for map display purposes. If required for ECRF and LVF purposes, Location Markers data MUST be included in the SiteStructureAddressPoint layer. Location Markers may represent locations such as an alarm box, a utility pole, a callbox, trail intersection, buoy, channel marker, or other similar feature. This dataset is referred to as the LocationMarkerPoint layer in in the GIS Layers and Indicators registry in Section 7.1 of NENA-STA-006 “GIS Layers and Indicators” Registry and in NENA documents going forward.
+          <t xml:space="preserve">Location Markers data is maintained as a point layer and is used primarily for map display purposes. If required for ECRF and LVF purposes, Location Markers data MUST be included in the SiteStructureAddressPoint layer. Location Markers may represent locations such as an alarm box, a utility pole, a callbox, a trail intersection, a buoy, a channel marker, or other similar features. This dataset is referred to as the LocationMarkerPoint layer in the GIS Layers and Indicators registry in the GIS Data Layers registry in Section 7.1 “GIS Data Layers” Registry and in NENA documents going forward.
 </t>
         </is>
       </c>

--- a/flatfile_templates/prebuilt_templates/v3.0/NG911_GISDataModelSchemaReport_v3.0.xlsx
+++ b/flatfile_templates/prebuilt_templates/v3.0/NG911_GISDataModelSchemaReport_v3.0.xlsx
@@ -14134,7 +14134,7 @@
     <row r="225">
       <c r="B225" t="inlineStr">
         <is>
-          <t>utility-box</t>
+          <t>utilitybox</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">

--- a/flatfile_templates/prebuilt_templates/v3.0/NG911_GISDataModelSchemaReport_v3.0.xlsx
+++ b/flatfile_templates/prebuilt_templates/v3.0/NG911_GISDataModelSchemaReport_v3.0.xlsx
@@ -11431,7 +11431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D744"/>
+  <dimension ref="A1:D740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14503,7 +14503,7 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>ServiceURI</t>
+          <t>ServiceURNSOS</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="D257" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">URI for call routing. This attribute is contained in the service boundary layers and will define the URI of the service.
+          <t xml:space="preserve">The SOS Service URN used to select the service for which a route is desired.
 </t>
         </is>
       </c>
@@ -14538,632 +14538,632 @@
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
-          <t>User Defined</t>
+          <t>urn:emergency:service:sos.psap</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>User Defined</t>
+          <t>PSAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>urn:emergency:service:sos.level_2_esrp</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Level 2 ESRP</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="6" t="inlineStr">
-        <is>
-          <t>ServiceURNSOS</t>
-        </is>
-      </c>
-      <c r="B261" s="6" t="inlineStr">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>urn:emergency:service:sos.level_3_esrp</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Level 3 ESRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>urn:emergency:service:sos.call_taker</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Call Taker</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr">
+        <is>
+          <t>ServiceURNResponder</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="inlineStr">
         <is>
           <t>CODED</t>
         </is>
       </c>
-      <c r="C261" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D261" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The SOS Service URN used to select the service for which a route is desired.
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D264" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Responder Service URN used to select the service for which a route is desired.
 </t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="B262" s="1" t="inlineStr">
+    <row r="265">
+      <c r="B265" s="1" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="C262" s="1" t="inlineStr">
+      <c r="C265" s="1" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>urn:emergency:service:sos.psap</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>PSAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>urn:emergency:service:sos.level_2_esrp</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Level 2 ESRP</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>urn:emergency:service:sos.level_3_esrp</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Level 3 ESRP</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t>urn:emergency:service:sos.call_taker</t>
+          <t>urn:emergency:service:responder.coast_guard</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Call Taker</t>
+          <t>Coast Guard Station</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>urn:emergency:service:responder.ems</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Emergency Medical Service</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>ServiceURNResponder</t>
-        </is>
-      </c>
-      <c r="B268" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C268" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D268" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Responder Service URN used to select the service for which a route is desired.
-</t>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>urn:emergency:service:responder.fire</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Fire Department</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="B269" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C269" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>urn:emergency:service:responder.mountain_rescue</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Mountain Rescue Service</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="B270" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.coast_guard</t>
+          <t>urn:emergency:service:responder.poison_control</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Coast Guard Station</t>
+          <t>Poison Control Center</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="B271" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.ems</t>
+          <t>urn:emergency:service:responder.police</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Emergency Medical Service</t>
+          <t>Police Agency</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="B272" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.fire</t>
+          <t>urn:emergency:service:responder.ems.air</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Fire Department</t>
+          <t>EMS - Air</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="B273" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.mountain_rescue</t>
+          <t>urn:emergency:service:responder.ems.tribal</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Mountain Rescue Service</t>
+          <t>EMS - Native American</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="B274" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.poison_control</t>
+          <t>urn:emergency:service:responder.ems.countyParish</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Poison Control Center</t>
+          <t>EMS - County or Parish</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="B275" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police</t>
+          <t>urn:emergency:service:responder.ems.local</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Police Agency</t>
+          <t>EMS - City, Town, Township, Borough, or Village</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="B276" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.ems.air</t>
+          <t>urn:emergency:service:responder.ems.private</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>EMS - Air</t>
+          <t>EMS - Contracted Ambulance Service</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.ems.tribal</t>
+          <t>urn:emergency:service:responder.ems.military</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>EMS - Native American</t>
+          <t>EMS - Military</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="B278" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.ems.countyParish</t>
+          <t>urn:emergency:service:responder.fire.airport</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>EMS - County or Parish</t>
+          <t>Fire - Airport Fire Service</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.ems.local</t>
+          <t>urn:emergency:service:responder.fire.forest</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>EMS - City, Town, Township, Borough, or Village</t>
+          <t>Fire - Forest Fire Service</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.ems.private</t>
+          <t>urn:emergency:service:responder.fire.military</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>EMS - Contracted Ambulance Service</t>
+          <t>Fire - Military</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="B281" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.ems.military</t>
+          <t>urn:emergency:service:responder.fire.private</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>EMS - Military</t>
+          <t>Fire - Private Fire Service</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="B282" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.fire.airport</t>
+          <t>urn:emergency:service:responder.police.countyParish</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Fire - Airport Fire Service</t>
+          <t>Police - County or Parish (not Sheriff)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="B283" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.fire.forest</t>
+          <t>urn:emergency:service:responder.police.federal</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Fire - Forest Fire Service</t>
+          <t>Police - Federal</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="B284" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.fire.military</t>
+          <t>urn:emergency:service:responder.police.local</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Fire - Military</t>
+          <t>Police - City, Town, Township, Borough, or Village</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="B285" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.fire.private</t>
+          <t>urn:emergency:service:responder.police.tribal</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Fire - Private Fire Service</t>
+          <t>Police - Native American</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="B286" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.countyParish</t>
+          <t>urn:emergency:service:responder.police.stateProvincial</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Police - County or Parish (not Sheriff)</t>
+          <t>Police - State/Provincial</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="B287" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal</t>
+          <t>urn:emergency:service:responder.police.sheriff</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Police - Federal</t>
+          <t>Police - Sheriff's Office</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="B288" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.local</t>
+          <t>urn:emergency:service:responder.police.campus</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Police - City, Town, Township, Borough, or Village</t>
+          <t>Police - Campus (Educational Institution)</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="B289" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.tribal</t>
+          <t>urn:emergency:service:responder.police.private</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Police - Native American</t>
+          <t>Police - Private (Non-governmental)</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="B290" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.stateProvincial</t>
+          <t>urn:emergency:service:responder.police.airport</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Police - State/Provincial</t>
+          <t>Police - Airport Authority</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="B291" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.sheriff</t>
+          <t>urn:emergency:service:responder.police.housing</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Police - Sheriff's Office</t>
+          <t>Police - Housing Authority</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="B292" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.campus</t>
+          <t>urn:emergency:service:responder.police.park</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Police - Campus (Educational Institution)</t>
+          <t>Police - Park</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="B293" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.private</t>
+          <t>urn:emergency:service:responder.police.military</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Police - Private (Non-governmental)</t>
+          <t>Police - Military</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="B294" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.airport</t>
+          <t>urn:emergency:service:responder.police.federal.atf</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Police - Airport Authority</t>
+          <t>Police Federal - Bureau of Alcohol Tobacco Fire Arms and Explosives</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="B295" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.housing</t>
+          <t>urn:emergency:service:responder.police.federal.cbp</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Police - Housing Authority</t>
+          <t>Police Federal - Customs and Border Protection</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="B296" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.park</t>
+          <t>urn:emergency:service:responder.police.federal.dss</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Police - Park</t>
+          <t>Police Federal - Diplomatic Security Service</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="B297" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.military</t>
+          <t>urn:emergency:service:responder.police.federal.dea</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Police - Military</t>
+          <t>Police Federal - Drug Enforcement Agency</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="B298" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal.atf</t>
+          <t>urn:emergency:service:responder.police.federal.fbi</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Police Federal - Bureau of Alcohol Tobacco Fire Arms and Explosives</t>
+          <t>Police Federal - Federal Bureau of Investigation</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="B299" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal.cbp</t>
+          <t>urn:emergency:service:responder.police.federal.fps</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Police Federal - Customs and Border Protection</t>
+          <t>Police Federal - Federal Protective Service</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="B300" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal.dss</t>
+          <t>urn:emergency:service:responder.police.federal.ice</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Police Federal - Diplomatic Security Service</t>
+          <t>Police Federal - Immigration and Customs Enforcement</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="B301" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal.dea</t>
+          <t>urn:emergency:service:responder.police.federal.marshal</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Police Federal - Drug Enforcement Agency</t>
+          <t>Police Federal - Marshals Service</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="B302" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal.fbi</t>
+          <t>urn:emergency:service:responder.police.federal.rcmp</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Police Federal - Federal Bureau of Investigation</t>
+          <t>Police Federal - Royal Canadian Mounted Police</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="B303" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal.fps</t>
+          <t>urn:emergency:service:responder.police.federal.pp</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Police Federal - Federal Protective Service</t>
+          <t>Police Federal - U.S. Park Police</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="B304" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal.ice</t>
+          <t>urn:emergency:service:responder.police.federal.usss</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Police Federal - Immigration and Customs Enforcement</t>
+          <t>Police Federal - U.S. Secret Service</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="B305" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.police.federal.marshal</t>
+          <t>urn:emergency:service:responder.psap</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Police Federal - Marshals Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>urn:emergency:service:responder.police.federal.rcmp</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Police Federal - Royal Canadian Mounted Police</t>
+          <t>Responder PSAP</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>urn:emergency:service:responder.police.federal.pp</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Police Federal - U.S. Park Police</t>
+      <c r="A307" s="6" t="inlineStr">
+        <is>
+          <t>SpeedLimit</t>
+        </is>
+      </c>
+      <c r="B307" s="6" t="inlineStr">
+        <is>
+          <t>RANGE</t>
+        </is>
+      </c>
+      <c r="C307" s="6" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="D307" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Posted Speed Limit in MPH or Km/h.
+</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>urn:emergency:service:responder.police.federal.usss</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Police Federal - U.S. Secret Service</t>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="B309" t="inlineStr">
         <is>
-          <t>urn:emergency:service:responder.psap</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Responder PSAP</t>
+          <t>999</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>SpeedLimit</t>
+          <t>StreetNameDirectional</t>
         </is>
       </c>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>RANGE</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="C311" s="6" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D311" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posted Speed Limit in MPH or Km/h.
+          <t xml:space="preserve">A word preceding or following the Street Name element that indicates the direction taken by the thoroughfare from an arbitrary starting point or line, or the sector where it is located.
 </t>
         </is>
       </c>
@@ -15171,5190 +15171,5143 @@
     <row r="312">
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Code</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="B313" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>North</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>North</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>South</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="6" t="inlineStr">
-        <is>
-          <t>StreetNameDirectional</t>
-        </is>
-      </c>
-      <c r="B315" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C315" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D315" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A word preceding or following the Street Name element that indicates the direction taken by the thoroughfare from an arbitrary starting point or line, or the sector where it is located.
-</t>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>East</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="B316" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C316" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>West</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="B317" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Northeast</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="B318" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Northwest</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Northwest</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="B319" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Southeast</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="B320" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Southwest</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="B321" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Nord</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Northeast</t>
+          <t>Nord</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="B322" t="inlineStr">
         <is>
-          <t>Northwest</t>
+          <t>Sud</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Northwest</t>
+          <t>Sud</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="B323" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Est</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Est</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="B324" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Ouest</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Southwest</t>
+          <t>Ouest</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="B325" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Nord-Est</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Nord</t>
+          <t>Nord-Est</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="B326" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord-Ouest</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Sud</t>
+          <t>Nord-Ouest</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="B327" t="inlineStr">
         <is>
-          <t>Est</t>
+          <t>Sud-Est</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Est</t>
+          <t>Sud-Est</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="B328" t="inlineStr">
         <is>
-          <t>Ouest</t>
+          <t>Sud-Ouest</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Ouest</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Nord-Est</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Nord-Est</t>
+          <t>Sud-Ouest</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Nord-Ouest</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Nord-Ouest</t>
+      <c r="A330" s="6" t="inlineStr">
+        <is>
+          <t>StreetNameType</t>
+        </is>
+      </c>
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="C330" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D330" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A word or phrase that precedes or follows the Street Name element and identifies a type of thoroughfare in a complete street name.
+</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Sud-Est</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Sud-Est</t>
+      <c r="B331" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C331" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="B332" t="inlineStr">
         <is>
-          <t>Sud-Ouest</t>
+          <t>Abbey</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Sud-Ouest</t>
+          <t>Abbey</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Access</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="6" t="inlineStr">
-        <is>
-          <t>StreetNameType</t>
-        </is>
-      </c>
-      <c r="B334" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C334" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D334" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A word or phrase that precedes or follows the Street Name element and identifies a type of thoroughfare in a complete street name.
-</t>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Access Road</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Access Road</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="B335" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C335" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Acres</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Acres</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="B336" t="inlineStr">
         <is>
-          <t>Abbey</t>
+          <t>Airport</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Abbey</t>
+          <t>Airport</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="B337" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Alcove</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Alcove</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="B338" t="inlineStr">
         <is>
-          <t>Access Road</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Access Road</t>
+          <t>Alle</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="B339" t="inlineStr">
         <is>
-          <t>Acres</t>
+          <t>Alley</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Acres</t>
+          <t>Alley</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="B340" t="inlineStr">
         <is>
-          <t>Airport</t>
+          <t>Annex</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Airport</t>
+          <t>Annex</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="B341" t="inlineStr">
         <is>
-          <t>Alcove</t>
+          <t>Approach</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Alcove</t>
+          <t>Approach</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="B342" t="inlineStr">
         <is>
-          <t>Alle</t>
+          <t>Arc</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Alle</t>
+          <t>Arc</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="B343" t="inlineStr">
         <is>
-          <t>Alley</t>
+          <t>Arcade</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Alley</t>
+          <t>Arcade</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="B344" t="inlineStr">
         <is>
-          <t>Annex</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Annex</t>
+          <t>Arch</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="B345" t="inlineStr">
         <is>
-          <t>Approach</t>
+          <t>Avenida</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Approach</t>
+          <t>Avenida</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="B346" t="inlineStr">
         <is>
-          <t>Arc</t>
+          <t>Avenue</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Arc</t>
+          <t>Avenue</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="B347" t="inlineStr">
         <is>
-          <t>Arcade</t>
+          <t>Avenue Circle</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Arcade</t>
+          <t>Avenue Circle</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="B348" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Avenue Court</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Arch</t>
+          <t>Avenue Court</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="B349" t="inlineStr">
         <is>
-          <t>Avenida</t>
+          <t>Avenue Loop</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Avenida</t>
+          <t>Avenue Loop</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="B350" t="inlineStr">
         <is>
-          <t>Avenue</t>
+          <t>Avenue Path</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Avenue</t>
+          <t>Avenue Path</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="B351" t="inlineStr">
         <is>
-          <t>Avenue Circle</t>
+          <t>Avenue Place</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Avenue Circle</t>
+          <t>Avenue Place</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="B352" t="inlineStr">
         <is>
-          <t>Avenue Court</t>
+          <t>Avenue Way</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Avenue Court</t>
+          <t>Avenue Way</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="B353" t="inlineStr">
         <is>
-          <t>Avenue Loop</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Avenue Loop</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="B354" t="inlineStr">
         <is>
-          <t>Avenue Path</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Avenue Path</t>
+          <t>Bay</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="B355" t="inlineStr">
         <is>
-          <t>Avenue Place</t>
+          <t>Bayou</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Avenue Place</t>
+          <t>Bayou</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="B356" t="inlineStr">
         <is>
-          <t>Avenue Way</t>
+          <t>Bayway</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Avenue Way</t>
+          <t>Bayway</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="B357" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="B358" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Bend</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Bend</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="B359" t="inlineStr">
         <is>
-          <t>Bayou</t>
+          <t>Bluff</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Bayou</t>
+          <t>Bluff</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="B360" t="inlineStr">
         <is>
-          <t>Bayway</t>
+          <t>Bluffs</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Bayway</t>
+          <t>Bluffs</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="B361" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Bottom</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="B362" t="inlineStr">
         <is>
-          <t>Bend</t>
+          <t>Boardwalk</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Bend</t>
+          <t>Boardwalk</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="B363" t="inlineStr">
         <is>
-          <t>Bluff</t>
+          <t>Boulevard</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Bluff</t>
+          <t>Boulevard</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="B364" t="inlineStr">
         <is>
-          <t>Bluffs</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Bluffs</t>
+          <t>Branch</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="B365" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Bridge</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Bridge</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="B366" t="inlineStr">
         <is>
-          <t>Boardwalk</t>
+          <t>Brook</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Boardwalk</t>
+          <t>Brook</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="B367" t="inlineStr">
         <is>
-          <t>Boulevard</t>
+          <t>Brooks</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Boulevard</t>
+          <t>Brooks</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="B368" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Bureau of Indian Affairs Route</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Bureau of Indian Affairs Route</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="B369" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Burg</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Burg</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="B370" t="inlineStr">
         <is>
-          <t>Brook</t>
+          <t>Burgs</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Brook</t>
+          <t>Burgs</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="B371" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Bypass</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>Bypass</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="B372" t="inlineStr">
         <is>
-          <t>Bureau of Indian Affairs Route</t>
+          <t>Calle</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Bureau of Indian Affairs Route</t>
+          <t>Calle</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="B373" t="inlineStr">
         <is>
-          <t>Burg</t>
+          <t>Callejon</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Burg</t>
+          <t>Callejon</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="B374" t="inlineStr">
         <is>
-          <t>Burgs</t>
+          <t>Camino</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Burgs</t>
+          <t>Camino</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="B375" t="inlineStr">
         <is>
-          <t>Bypass</t>
+          <t>Camp</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Bypass</t>
+          <t>Camp</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="B376" t="inlineStr">
         <is>
-          <t>Calle</t>
+          <t>Canyon</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Calle</t>
+          <t>Canyon</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="B377" t="inlineStr">
         <is>
-          <t>Callejon</t>
+          <t>Cape</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Callejon</t>
+          <t>Cape</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="B378" t="inlineStr">
         <is>
-          <t>Camino</t>
+          <t>Cartway</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Camino</t>
+          <t>Cartway</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="B379" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Causeway</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Camp</t>
+          <t>Causeway</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="B380" t="inlineStr">
         <is>
-          <t>Canyon</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Canyon</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="B381" t="inlineStr">
         <is>
-          <t>Cape</t>
+          <t>Centers</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Cape</t>
+          <t>Centers</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="B382" t="inlineStr">
         <is>
-          <t>Cartway</t>
+          <t>Centre</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Cartway</t>
+          <t>Centre</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="B383" t="inlineStr">
         <is>
-          <t>Causeway</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Causeway</t>
+          <t>Channel</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="B384" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Chase</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Chase</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="B385" t="inlineStr">
         <is>
-          <t>Centers</t>
+          <t>Chemin</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Centers</t>
+          <t>Chemin</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="B386" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Centre</t>
+          <t>Circle</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="B387" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Circles</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Circles</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="B388" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Circus</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Circus</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="B389" t="inlineStr">
         <is>
-          <t>Chemin</t>
+          <t>Cliff</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Chemin</t>
+          <t>Cliff</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="B390" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Cliffs</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Cliffs</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="B391" t="inlineStr">
         <is>
-          <t>Circles</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Circles</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="B392" t="inlineStr">
         <is>
-          <t>Circus</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Circus</t>
+          <t>Club</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="B393" t="inlineStr">
         <is>
-          <t>Cliff</t>
+          <t>Cluster</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Cliff</t>
+          <t>Cluster</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="B394" t="inlineStr">
         <is>
-          <t>Cliffs</t>
+          <t>Coast Highway</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Cliffs</t>
+          <t>Coast Highway</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="B395" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Common</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="B396" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Commons</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Commons</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="B397" t="inlineStr">
         <is>
-          <t>Cluster</t>
+          <t>Concession Road</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Cluster</t>
+          <t>Concession Road</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="B398" t="inlineStr">
         <is>
-          <t>Coast Highway</t>
+          <t>Concourse</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Coast Highway</t>
+          <t>Concourse</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="B399" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Connect</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Connect</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="B400" t="inlineStr">
         <is>
-          <t>Commons</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Commons</t>
+          <t>Connector</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="B401" t="inlineStr">
         <is>
-          <t>Concession Road</t>
+          <t>Corner</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Concession Road</t>
+          <t>Corner</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="B402" t="inlineStr">
         <is>
-          <t>Concourse</t>
+          <t>Corners</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Concourse</t>
+          <t>Corners</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="B403" t="inlineStr">
         <is>
-          <t>Connect</t>
+          <t>Corridor</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Connect</t>
+          <t>Corridor</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="B404" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Corso</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Corso</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="B405" t="inlineStr">
         <is>
-          <t>Corner</t>
+          <t>Corte</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Corner</t>
+          <t>Corte</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="B406" t="inlineStr">
         <is>
-          <t>Corners</t>
+          <t>County Forest Road</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Corners</t>
+          <t>County Forest Road</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="B407" t="inlineStr">
         <is>
-          <t>Corridor</t>
+          <t>County Highway</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Corridor</t>
+          <t>County Highway</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="B408" t="inlineStr">
         <is>
-          <t>Corso</t>
+          <t>County Road</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Corso</t>
+          <t>County Road</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="B409" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>County Route</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Corte</t>
+          <t>County Route</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="B410" t="inlineStr">
         <is>
-          <t>County Forest Road</t>
+          <t>County State Aid Highway</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>County Forest Road</t>
+          <t>County State Aid Highway</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="B411" t="inlineStr">
         <is>
-          <t>County Highway</t>
+          <t>Cours</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>County Highway</t>
+          <t>Cours</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="B412" t="inlineStr">
         <is>
-          <t>County Road</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>County Road</t>
+          <t>Course</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="B413" t="inlineStr">
         <is>
-          <t>County Route</t>
+          <t>Court</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>County Route</t>
+          <t>Court</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="B414" t="inlineStr">
         <is>
-          <t>County State Aid Highway</t>
+          <t>Courts</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>County State Aid Highway</t>
+          <t>Courts</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="B415" t="inlineStr">
         <is>
-          <t>Cours</t>
+          <t>Cove</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Cours</t>
+          <t>Cove</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="B416" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Coves</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Coves</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="B417" t="inlineStr">
         <is>
-          <t>Court</t>
+          <t>Creek</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Court</t>
+          <t>Creek</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="B418" t="inlineStr">
         <is>
-          <t>Courts</t>
+          <t>Crescent</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Courts</t>
+          <t>Crescent</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="B419" t="inlineStr">
         <is>
-          <t>Cove</t>
+          <t>Crest</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Cove</t>
+          <t>Crest</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="B420" t="inlineStr">
         <is>
-          <t>Coves</t>
+          <t>Cross</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Coves</t>
+          <t>Cross</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="B421" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Crossing</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Crossing</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="B422" t="inlineStr">
         <is>
-          <t>Crescent</t>
+          <t>Crossings</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Crescent</t>
+          <t>Crossings</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="B423" t="inlineStr">
         <is>
-          <t>Crest</t>
+          <t>Crossover</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Crest</t>
+          <t>Crossover</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="B424" t="inlineStr">
         <is>
-          <t>Cross</t>
+          <t>Crossroad</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Cross</t>
+          <t>Crossroad</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="B425" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Crossroads</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Crossing</t>
+          <t>Crossroads</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="B426" t="inlineStr">
         <is>
-          <t>Crossings</t>
+          <t>Crossway</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Crossings</t>
+          <t>Crossway</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="B427" t="inlineStr">
         <is>
-          <t>Crossover</t>
+          <t>Curve</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Crossover</t>
+          <t>Curve</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="B428" t="inlineStr">
         <is>
-          <t>Crossroad</t>
+          <t>Custer County Road</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Crossroad</t>
+          <t>Custer County Road</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="B429" t="inlineStr">
         <is>
-          <t>Crossroads</t>
+          <t>Cutoff</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Crossroads</t>
+          <t>Cutoff</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="B430" t="inlineStr">
         <is>
-          <t>Crossway</t>
+          <t>Cutting</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Crossway</t>
+          <t>Cutting</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="B431" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Dale</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Curve</t>
+          <t>Dale</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="B432" t="inlineStr">
         <is>
-          <t>Custer County Road</t>
+          <t>Dam</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Custer County Road</t>
+          <t>Dam</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="B433" t="inlineStr">
         <is>
-          <t>Cutoff</t>
+          <t>Dawson County Road</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Cutoff</t>
+          <t>Dawson County Road</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="B434" t="inlineStr">
         <is>
-          <t>Cutting</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Cutting</t>
+          <t>Dell</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="B435" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Divide</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Divide</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="B436" t="inlineStr">
         <is>
-          <t>Dam</t>
+          <t>Dock</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Dam</t>
+          <t>Dock</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="B437" t="inlineStr">
         <is>
-          <t>Dawson County Road</t>
+          <t>Down</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Dawson County Road</t>
+          <t>Down</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="B438" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Downs</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Downs</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="B439" t="inlineStr">
         <is>
-          <t>Divide</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Divide</t>
+          <t>Draw</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="B440" t="inlineStr">
         <is>
-          <t>Dock</t>
+          <t>Drift</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Dock</t>
+          <t>Drift</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="B441" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Down</t>
+          <t>Drive</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="B442" t="inlineStr">
         <is>
-          <t>Downs</t>
+          <t>Drives</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Downs</t>
+          <t>Drives</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="B443" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Driveway</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Driveway</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="B444" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Dugway</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Dugway</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="B445" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>Echo</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>Echo</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="B446" t="inlineStr">
         <is>
-          <t>Drives</t>
+          <t>Edge</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Drives</t>
+          <t>Edge</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="B447" t="inlineStr">
         <is>
-          <t>Driveway</t>
+          <t>End</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Driveway</t>
+          <t>End</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="B448" t="inlineStr">
         <is>
-          <t>Dugway</t>
+          <t>Entrance</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Dugway</t>
+          <t>Entrance</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="B449" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Entry</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Entry</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="B450" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Esplanade</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>Esplanade</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="B451" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Estate</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Estate</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="B452" t="inlineStr">
         <is>
-          <t>Entrance</t>
+          <t>Estates</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Entrance</t>
+          <t>Estates</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="B453" t="inlineStr">
         <is>
-          <t>Entry</t>
+          <t>Exchange</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Entry</t>
+          <t>Exchange</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="B454" t="inlineStr">
         <is>
-          <t>Esplanade</t>
+          <t>Exit</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Esplanade</t>
+          <t>Exit</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="B455" t="inlineStr">
         <is>
-          <t>Estate</t>
+          <t>Expressway</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Estate</t>
+          <t>Expressway</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="B456" t="inlineStr">
         <is>
-          <t>Estates</t>
+          <t>Extension</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Estates</t>
+          <t>Extension</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="B457" t="inlineStr">
         <is>
-          <t>Exchange</t>
+          <t>Extensions</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Exchange</t>
+          <t>Extensions</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="B458" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Fall</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="B459" t="inlineStr">
         <is>
-          <t>Expressway</t>
+          <t>Falls</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Expressway</t>
+          <t>Falls</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="B460" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Fare</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Fare</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="B461" t="inlineStr">
         <is>
-          <t>Extensions</t>
+          <t>Farm</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Extensions</t>
+          <t>Farm</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="B462" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Farm to Market</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Farm to Market</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="B463" t="inlineStr">
         <is>
-          <t>Falls</t>
+          <t>Federal-Aid Secondary Highway</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Falls</t>
+          <t>Federal-Aid Secondary Highway</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="B464" t="inlineStr">
         <is>
-          <t>Fare</t>
+          <t>Ferry</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Fare</t>
+          <t>Ferry</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="B465" t="inlineStr">
         <is>
-          <t>Farm</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Farm</t>
+          <t>Field</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="B466" t="inlineStr">
         <is>
-          <t>Farm to Market</t>
+          <t>Fields</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Farm to Market</t>
+          <t>Fields</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="B467" t="inlineStr">
         <is>
-          <t>Federal-Aid Secondary Highway</t>
+          <t>Flat</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Federal-Aid Secondary Highway</t>
+          <t>Flat</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="B468" t="inlineStr">
         <is>
-          <t>Ferry</t>
+          <t>Flats</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Ferry</t>
+          <t>Flats</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="B469" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Flowage</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Flowage</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="B470" t="inlineStr">
         <is>
-          <t>Fields</t>
+          <t>Flyway</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Fields</t>
+          <t>Flyway</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="B471" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>Ford</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="B472" t="inlineStr">
         <is>
-          <t>Flats</t>
+          <t>Fords</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Flats</t>
+          <t>Fords</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="B473" t="inlineStr">
         <is>
-          <t>Flowage</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Flowage</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="B474" t="inlineStr">
         <is>
-          <t>Flyway</t>
+          <t>Forest Highway</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Flyway</t>
+          <t>Forest Highway</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="B475" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Forest Road</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Forest Road</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="B476" t="inlineStr">
         <is>
-          <t>Fords</t>
+          <t>Forge</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Fords</t>
+          <t>Forge</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="B477" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Forges</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Forges</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="B478" t="inlineStr">
         <is>
-          <t>Forest Highway</t>
+          <t>Fork</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Forest Highway</t>
+          <t>Fork</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="B479" t="inlineStr">
         <is>
-          <t>Forest Road</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Forest Road</t>
+          <t>Forks</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="B480" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Fort</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Forge</t>
+          <t>Fort</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="B481" t="inlineStr">
         <is>
-          <t>Forges</t>
+          <t>Freeway</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Forges</t>
+          <t>Freeway</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="B482" t="inlineStr">
         <is>
-          <t>Fork</t>
+          <t>Front</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Fork</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="B483" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Frontage Road</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Frontage Road</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="B484" t="inlineStr">
         <is>
-          <t>Fort</t>
+          <t>Gables</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Fort</t>
+          <t>Gables</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="B485" t="inlineStr">
         <is>
-          <t>Freeway</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Freeway</t>
+          <t>Garden</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="B486" t="inlineStr">
         <is>
-          <t>Front</t>
+          <t>Gardens</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Front</t>
+          <t>Gardens</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="B487" t="inlineStr">
         <is>
-          <t>Frontage Road</t>
+          <t>Garth</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Frontage Road</t>
+          <t>Garth</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="B488" t="inlineStr">
         <is>
-          <t>Gables</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Gables</t>
+          <t>Gate</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="B489" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Gates</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Gates</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="B490" t="inlineStr">
         <is>
-          <t>Gardens</t>
+          <t>Gateway</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Gardens</t>
+          <t>Gateway</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="B491" t="inlineStr">
         <is>
-          <t>Garth</t>
+          <t>Glade</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Garth</t>
+          <t>Glade</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="B492" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Glen</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Glen</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="B493" t="inlineStr">
         <is>
-          <t>Gates</t>
+          <t>Glens</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Gates</t>
+          <t>Glens</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="B494" t="inlineStr">
         <is>
-          <t>Gateway</t>
+          <t>Gorge</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Gateway</t>
+          <t>Gorge</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="B495" t="inlineStr">
         <is>
-          <t>Glade</t>
+          <t>Grade</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Glade</t>
+          <t>Grade</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="B496" t="inlineStr">
         <is>
-          <t>Glen</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Glen</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="B497" t="inlineStr">
         <is>
-          <t>Glens</t>
+          <t>Greens</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Glens</t>
+          <t>Greens</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="B498" t="inlineStr">
         <is>
-          <t>Gorge</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Gorge</t>
+          <t>Greenway</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="B499" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>Grove</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Grade</t>
+          <t>Grove</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="B500" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Groves</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Groves</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="B501" t="inlineStr">
         <is>
-          <t>Greens</t>
+          <t>Harbor</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Greens</t>
+          <t>Harbor</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="B502" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Harbors</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Harbors</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="B503" t="inlineStr">
         <is>
-          <t>Grove</t>
+          <t>Harbour</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Grove</t>
+          <t>Harbour</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="B504" t="inlineStr">
         <is>
-          <t>Groves</t>
+          <t>Haul Road</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Groves</t>
+          <t>Haul Road</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="B505" t="inlineStr">
         <is>
-          <t>Harbor</t>
+          <t>Haven</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Harbor</t>
+          <t>Haven</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="B506" t="inlineStr">
         <is>
-          <t>Harbors</t>
+          <t>Heath</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Harbors</t>
+          <t>Heath</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="B507" t="inlineStr">
         <is>
-          <t>Harbour</t>
+          <t>Heights</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Harbour</t>
+          <t>Heights</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="B508" t="inlineStr">
         <is>
-          <t>Haul Road</t>
+          <t>Hideaway</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Haul Road</t>
+          <t>Hideaway</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="B509" t="inlineStr">
         <is>
-          <t>Haven</t>
+          <t>Highway</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Haven</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="B510" t="inlineStr">
         <is>
-          <t>Heath</t>
+          <t>Hill</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Heath</t>
+          <t>Hill</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="B511" t="inlineStr">
         <is>
-          <t>Heights</t>
+          <t>Hills</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Heights</t>
+          <t>Hills</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="B512" t="inlineStr">
         <is>
-          <t>Hideaway</t>
+          <t>Hollow</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Hideaway</t>
+          <t>Hollow</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="B513" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Horn</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Horn</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="B514" t="inlineStr">
         <is>
-          <t>Hill</t>
+          <t>Horseshoe</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Hill</t>
+          <t>Horseshoe</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="B515" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Indian Service Road</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Hills</t>
+          <t>Indian Service Road</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="B516" t="inlineStr">
         <is>
-          <t>Hollow</t>
+          <t>Inlet</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Hollow</t>
+          <t>Inlet</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="B517" t="inlineStr">
         <is>
-          <t>Horn</t>
+          <t>Interstate</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Horn</t>
+          <t>Interstate</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="B518" t="inlineStr">
         <is>
-          <t>Horseshoe</t>
+          <t>Interval</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Horseshoe</t>
+          <t>Interval</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="B519" t="inlineStr">
         <is>
-          <t>Indian Service Road</t>
+          <t>Island</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Indian Service Road</t>
+          <t>Island</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="B520" t="inlineStr">
         <is>
-          <t>Inlet</t>
+          <t>Islands</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Inlet</t>
+          <t>Islands</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="B521" t="inlineStr">
         <is>
-          <t>Interstate</t>
+          <t>Isle</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Interstate</t>
+          <t>Isle</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="B522" t="inlineStr">
         <is>
-          <t>Interval</t>
+          <t>Isles</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Interval</t>
+          <t>Isles</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="B523" t="inlineStr">
         <is>
-          <t>Island</t>
+          <t>J-Turn</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Island</t>
+          <t>J-Turn</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="B524" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>Junction</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>Junction</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="B525" t="inlineStr">
         <is>
-          <t>Isle</t>
+          <t>Junctions</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Isle</t>
+          <t>Junctions</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="B526" t="inlineStr">
         <is>
-          <t>Isles</t>
+          <t>Keep</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Isles</t>
+          <t>Keep</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="B527" t="inlineStr">
         <is>
-          <t>J-Turn</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>J-Turn</t>
+          <t>Key</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="B528" t="inlineStr">
         <is>
-          <t>Junction</t>
+          <t>Keys</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Junction</t>
+          <t>Keys</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="B529" t="inlineStr">
         <is>
-          <t>Junctions</t>
+          <t>Knoll</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Junctions</t>
+          <t>Knoll</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="B530" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Knolls</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Keep</t>
+          <t>Knolls</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="B531" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Lair</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Lair</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="B532" t="inlineStr">
         <is>
-          <t>Keys</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Keys</t>
+          <t>Lake</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="B533" t="inlineStr">
         <is>
-          <t>Knoll</t>
+          <t>Lakes</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Knoll</t>
+          <t>Lakes</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="B534" t="inlineStr">
         <is>
-          <t>Knolls</t>
+          <t>Land</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Knolls</t>
+          <t>Land</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="B535" t="inlineStr">
         <is>
-          <t>Lair</t>
+          <t>Landing</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Lair</t>
+          <t>Landing</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="B536" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Lane</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Lane</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="B537" t="inlineStr">
         <is>
-          <t>Lakes</t>
+          <t>Lane Circle</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Lakes</t>
+          <t>Lane Circle</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="B538" t="inlineStr">
         <is>
-          <t>Land</t>
+          <t>Lane Court</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Land</t>
+          <t>Lane Court</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="B539" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Lane Road</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Landing</t>
+          <t>Lane Road</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="B540" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Lane</t>
+          <t>Lateral</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="B541" t="inlineStr">
         <is>
-          <t>Lane Circle</t>
+          <t>Ledge</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Lane Circle</t>
+          <t>Ledge</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="B542" t="inlineStr">
         <is>
-          <t>Lane Court</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Lane Court</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="B543" t="inlineStr">
         <is>
-          <t>Lane Road</t>
+          <t>Lights</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Lane Road</t>
+          <t>Lights</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="B544" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Line</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="B545" t="inlineStr">
         <is>
-          <t>Ledge</t>
+          <t>Loaf</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Ledge</t>
+          <t>Loaf</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="B546" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Lock</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="B547" t="inlineStr">
         <is>
-          <t>Lights</t>
+          <t>Locks</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Lights</t>
+          <t>Locks</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="B548" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Lodge</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Lodge</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="B549" t="inlineStr">
         <is>
-          <t>Loaf</t>
+          <t>Lookout</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Loaf</t>
+          <t>Lookout</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="B550" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Loop</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Loop</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="B551" t="inlineStr">
         <is>
-          <t>Locks</t>
+          <t>Loop Road</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Locks</t>
+          <t>Loop Road</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="B552" t="inlineStr">
         <is>
-          <t>Lodge</t>
+          <t>Lugar</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Lodge</t>
+          <t>Lugar</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="B553" t="inlineStr">
         <is>
-          <t>Lookout</t>
+          <t>Mall</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Lookout</t>
+          <t>Mall</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="B554" t="inlineStr">
         <is>
-          <t>Loop</t>
+          <t>Manor</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Loop</t>
+          <t>Manor</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="B555" t="inlineStr">
         <is>
-          <t>Loop Road</t>
+          <t>Manors</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Loop Road</t>
+          <t>Manors</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="B556" t="inlineStr">
         <is>
-          <t>Lugar</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Lugar</t>
+          <t>Market</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="B557" t="inlineStr">
         <is>
-          <t>Mall</t>
+          <t>Meadow</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Mall</t>
+          <t>Meadow</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="B558" t="inlineStr">
         <is>
-          <t>Manor</t>
+          <t>Meadows</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Manor</t>
+          <t>Meadows</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="B559" t="inlineStr">
         <is>
-          <t>Manors</t>
+          <t>Mews</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Manors</t>
+          <t>Mews</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="B560" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Mill</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Market</t>
+          <t>Mill</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="B561" t="inlineStr">
         <is>
-          <t>Meadow</t>
+          <t>Mills</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Meadow</t>
+          <t>Mills</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="B562" t="inlineStr">
         <is>
-          <t>Meadows</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Meadows</t>
+          <t>Mission</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="B563" t="inlineStr">
         <is>
-          <t>Mews</t>
+          <t>Montana Highway</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Mews</t>
+          <t>Montana Highway</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="B564" t="inlineStr">
         <is>
-          <t>Mill</t>
+          <t>Motorway</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Mill</t>
+          <t>Motorway</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="B565" t="inlineStr">
         <is>
-          <t>Mills</t>
+          <t>Mount</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Mills</t>
+          <t>Mount</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="B566" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Mountain</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="B567" t="inlineStr">
         <is>
-          <t>Montana Highway</t>
+          <t>Mountains</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Montana Highway</t>
+          <t>Mountains</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="B568" t="inlineStr">
         <is>
-          <t>Motorway</t>
+          <t>Narrows</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Motorway</t>
+          <t>Narrows</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="B569" t="inlineStr">
         <is>
-          <t>Mount</t>
+          <t>National Forest Development Road</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Mount</t>
+          <t>National Forest Development Road</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="B570" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Neck</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Neck</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="B571" t="inlineStr">
         <is>
-          <t>Mountains</t>
+          <t>Nook</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Mountains</t>
+          <t>Nook</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="B572" t="inlineStr">
         <is>
-          <t>Narrows</t>
+          <t>North Carolina Highway</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Narrows</t>
+          <t>North Carolina Highway</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="B573" t="inlineStr">
         <is>
-          <t>National Forest Development Road</t>
+          <t>Oaks</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>National Forest Development Road</t>
+          <t>Oaks</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="B574" t="inlineStr">
         <is>
-          <t>Neck</t>
+          <t>Old County Road</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Neck</t>
+          <t>Old County Road</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="B575" t="inlineStr">
         <is>
-          <t>Nook</t>
+          <t>Orchard</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Nook</t>
+          <t>Orchard</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="B576" t="inlineStr">
         <is>
-          <t>North Carolina Highway</t>
+          <t>Oval</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>North Carolina Highway</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="B577" t="inlineStr">
         <is>
-          <t>Oaks</t>
+          <t>Overlook</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Oaks</t>
+          <t>Overlook</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="B578" t="inlineStr">
         <is>
-          <t>Old County Road</t>
+          <t>Overpass</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Old County Road</t>
+          <t>Overpass</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="B579" t="inlineStr">
         <is>
-          <t>Orchard</t>
+          <t>Ovi</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Orchard</t>
+          <t>Ovi</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="B580" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Oval</t>
+          <t>Park</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="B581" t="inlineStr">
         <is>
-          <t>Overlook</t>
+          <t>Parke</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Overlook</t>
+          <t>Parke</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="B582" t="inlineStr">
         <is>
-          <t>Overpass</t>
+          <t>Parks</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Overpass</t>
+          <t>Parks</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="B583" t="inlineStr">
         <is>
-          <t>Ovi</t>
+          <t>Parkway</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Ovi</t>
+          <t>Parkway</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="B584" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Parkways</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Parkways</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="B585" t="inlineStr">
         <is>
-          <t>Parke</t>
+          <t>Paseo</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Parke</t>
+          <t>Paseo</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="B586" t="inlineStr">
         <is>
-          <t>Parks</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Parks</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="B587" t="inlineStr">
         <is>
-          <t>Parkway</t>
+          <t>Passage</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Parkway</t>
+          <t>Passage</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="B588" t="inlineStr">
         <is>
-          <t>Parkways</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Parkways</t>
+          <t>Path</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="B589" t="inlineStr">
         <is>
-          <t>Paseo</t>
+          <t>Pathway</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Paseo</t>
+          <t>Pathway</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="B590" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Piazza</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Piazza</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="B591" t="inlineStr">
         <is>
-          <t>Passage</t>
+          <t>Pike</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Passage</t>
+          <t>Pike</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="B592" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Pine</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Pine</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="B593" t="inlineStr">
         <is>
-          <t>Pathway</t>
+          <t>Pines</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Pathway</t>
+          <t>Pines</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="B594" t="inlineStr">
         <is>
-          <t>Piazza</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Piazza</t>
+          <t>Place</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="B595" t="inlineStr">
         <is>
-          <t>Pike</t>
+          <t>Placita</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Pike</t>
+          <t>Placita</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="B596" t="inlineStr">
         <is>
-          <t>Pine</t>
+          <t>Plain</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Pine</t>
+          <t>Plain</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="B597" t="inlineStr">
         <is>
-          <t>Pines</t>
+          <t>Plains</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Pines</t>
+          <t>Plains</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="B598" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Platz</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Platz</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="B599" t="inlineStr">
         <is>
-          <t>Placita</t>
+          <t>Plaza</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Placita</t>
+          <t>Plaza</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="B600" t="inlineStr">
         <is>
-          <t>Plain</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Plain</t>
+          <t>Point</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="B601" t="inlineStr">
         <is>
-          <t>Plains</t>
+          <t>Pointe</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Plains</t>
+          <t>Pointe</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="B602" t="inlineStr">
         <is>
-          <t>Platz</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Platz</t>
+          <t>Points</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="B603" t="inlineStr">
         <is>
-          <t>Plaza</t>
+          <t>Port</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Plaza</t>
+          <t>Port</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="B604" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Ports</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Ports</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="B605" t="inlineStr">
         <is>
-          <t>Pointe</t>
+          <t>Prairie</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Pointe</t>
+          <t>Prairie</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="B606" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Private Road</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Private Road</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="B607" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Promenade</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Port</t>
+          <t>Promenade</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="B608" t="inlineStr">
         <is>
-          <t>Ports</t>
+          <t>Public Access</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Ports</t>
+          <t>Public Access</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="B609" t="inlineStr">
         <is>
-          <t>Prairie</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Prairie</t>
+          <t>Quarter</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="B610" t="inlineStr">
         <is>
-          <t>Private Road</t>
+          <t>Quay</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Private Road</t>
+          <t>Quay</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="B611" t="inlineStr">
         <is>
-          <t>Promenade</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Promenade</t>
+          <t>Ramp</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="B612" t="inlineStr">
         <is>
-          <t>Public Access</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Public Access</t>
+          <t>Radial</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="B613" t="inlineStr">
         <is>
-          <t>Quarter</t>
+          <t>Ranch</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Quarter</t>
+          <t>Ranch</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="B614" t="inlineStr">
         <is>
-          <t>Quay</t>
+          <t>Rancho</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Quay</t>
+          <t>Rancho</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="B615" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Rapid</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Rapid</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="B616" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Rapids</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>Rapids</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="B617" t="inlineStr">
         <is>
-          <t>Ranch</t>
+          <t>Reach</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Ranch</t>
+          <t>Reach</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="B618" t="inlineStr">
         <is>
-          <t>Rancho</t>
+          <t>Recreational Road</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Rancho</t>
+          <t>Recreational Road</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="B619" t="inlineStr">
         <is>
-          <t>Rapid</t>
+          <t>Rest</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Rapid</t>
+          <t>Rest</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="B620" t="inlineStr">
         <is>
-          <t>Rapids</t>
+          <t>Retreat</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Rapids</t>
+          <t>Retreat</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="B621" t="inlineStr">
         <is>
-          <t>Reach</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Reach</t>
+          <t>Ridge</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="B622" t="inlineStr">
         <is>
-          <t>Recreational Road</t>
+          <t>Ridges</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Recreational Road</t>
+          <t>Ridges</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="B623" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Rise</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Rise</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="B624" t="inlineStr">
         <is>
-          <t>Retreat</t>
+          <t>River</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Retreat</t>
+          <t>River</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="B625" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>River Road</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>River Road</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="B626" t="inlineStr">
         <is>
-          <t>Ridges</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Ridges</t>
+          <t>Road</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="B627" t="inlineStr">
         <is>
-          <t>Rise</t>
+          <t>Roads</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Rise</t>
+          <t>Roads</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="B628" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Round</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="B629" t="inlineStr">
         <is>
-          <t>River Road</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>River Road</t>
+          <t>Route</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="B630" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Row</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="B631" t="inlineStr">
         <is>
-          <t>Roads</t>
+          <t>Rue</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Roads</t>
+          <t>Rue</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="B632" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Run</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="B633" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Runne</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Runne</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="B634" t="inlineStr">
         <is>
-          <t>Row</t>
+          <t>Runway</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Row</t>
+          <t>Runway</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="B635" t="inlineStr">
         <is>
-          <t>Rue</t>
+          <t>Shoal</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Rue</t>
+          <t>Shoal</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="B636" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>Shoals</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Run</t>
+          <t>Shoals</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="B637" t="inlineStr">
         <is>
-          <t>Runne</t>
+          <t>Shore</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Runne</t>
+          <t>Shore</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="B638" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>Shores</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>Shores</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="B639" t="inlineStr">
         <is>
-          <t>Shoal</t>
+          <t>Sideroad</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Shoal</t>
+          <t>Sideroad</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="B640" t="inlineStr">
         <is>
-          <t>Shoals</t>
+          <t>Skies</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Shoals</t>
+          <t>Skies</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="B641" t="inlineStr">
         <is>
-          <t>Shore</t>
+          <t>Skyway</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Shore</t>
+          <t>Skyway</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="B642" t="inlineStr">
         <is>
-          <t>Shores</t>
+          <t>Slip</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Shores</t>
+          <t>Slip</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="B643" t="inlineStr">
         <is>
-          <t>Sideroad</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Sideroad</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="B644" t="inlineStr">
         <is>
-          <t>Skies</t>
+          <t>Springs</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Skies</t>
+          <t>Springs</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="B645" t="inlineStr">
         <is>
-          <t>Skyway</t>
+          <t>Spur</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Skyway</t>
+          <t>Spur</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="B646" t="inlineStr">
         <is>
-          <t>Slip</t>
+          <t>Spurs</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Slip</t>
+          <t>Spurs</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="B647" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="B648" t="inlineStr">
         <is>
-          <t>Springs</t>
+          <t>Squares</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Springs</t>
+          <t>Squares</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="B649" t="inlineStr">
         <is>
-          <t>Spur</t>
+          <t>State Highway</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Spur</t>
+          <t>State Highway</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="B650" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>State Park Road</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>State Park Road</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="B651" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>State Parkway</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>State Parkway</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="B652" t="inlineStr">
         <is>
-          <t>Squares</t>
+          <t>State Road</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Squares</t>
+          <t>State Road</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="B653" t="inlineStr">
         <is>
-          <t>State Highway</t>
+          <t>State Route</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>State Highway</t>
+          <t>State Route</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="B654" t="inlineStr">
         <is>
-          <t>State Park Road</t>
+          <t>State Secondary</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>State Park Road</t>
+          <t>State Secondary</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="B655" t="inlineStr">
         <is>
-          <t>State Parkway</t>
+          <t>State Spur</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>State Parkway</t>
+          <t>State Spur</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="B656" t="inlineStr">
         <is>
-          <t>State Road</t>
+          <t>Station</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>State Road</t>
+          <t>Station</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="B657" t="inlineStr">
         <is>
-          <t>State Route</t>
+          <t>Strand</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>State Route</t>
+          <t>Strand</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="B658" t="inlineStr">
         <is>
-          <t>State Secondary</t>
+          <t>Strasse</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>State Secondary</t>
+          <t>Strasse</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="B659" t="inlineStr">
         <is>
-          <t>State Spur</t>
+          <t>Stravenue</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>State Spur</t>
+          <t>Stravenue</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="B660" t="inlineStr">
         <is>
-          <t>Station</t>
+          <t>Stream</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Station</t>
+          <t>Stream</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="B661" t="inlineStr">
         <is>
-          <t>Strand</t>
+          <t>Street</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Strand</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="B662" t="inlineStr">
         <is>
-          <t>Strasse</t>
+          <t>Streets</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Strasse</t>
+          <t>Streets</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="B663" t="inlineStr">
         <is>
-          <t>Stravenue</t>
+          <t>Street Circle</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Stravenue</t>
+          <t>Street Circle</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="B664" t="inlineStr">
         <is>
-          <t>Stream</t>
+          <t>Street Court</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Stream</t>
+          <t>Street Court</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="B665" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Street Loop</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Street Loop</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="B666" t="inlineStr">
         <is>
-          <t>Streets</t>
+          <t>Street Path</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Streets</t>
+          <t>Street Path</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="B667" t="inlineStr">
         <is>
-          <t>Street Circle</t>
+          <t>Street Place</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Street Circle</t>
+          <t>Street Place</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="B668" t="inlineStr">
         <is>
-          <t>Street Court</t>
+          <t>Street Way</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Street Court</t>
+          <t>Street Way</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="B669" t="inlineStr">
         <is>
-          <t>Street Loop</t>
+          <t>Strip</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Street Loop</t>
+          <t>Strip</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="B670" t="inlineStr">
         <is>
-          <t>Street Path</t>
+          <t>Summit</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Street Path</t>
+          <t>Summit</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="B671" t="inlineStr">
         <is>
-          <t>Street Place</t>
+          <t>Taxiway</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Street Place</t>
+          <t>Taxiway</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="B672" t="inlineStr">
         <is>
-          <t>Street Way</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Street Way</t>
+          <t>Terminal</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="B673" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Tern</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Strip</t>
+          <t>Tern</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="B674" t="inlineStr">
         <is>
-          <t>Summit</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Summit</t>
+          <t>Terrace</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="B675" t="inlineStr">
         <is>
-          <t>Taxiway</t>
+          <t>Throughway</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Taxiway</t>
+          <t>Throughway</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="B676" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Thruway</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Thruway</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="B677" t="inlineStr">
         <is>
-          <t>Tern</t>
+          <t>Timber Road</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Tern</t>
+          <t>Timber Road</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="B678" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Townline</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Townline</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="B679" t="inlineStr">
         <is>
-          <t>Throughway</t>
+          <t>Town Road</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Throughway</t>
+          <t>Town Road</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="B680" t="inlineStr">
         <is>
-          <t>Thruway</t>
+          <t>Township Road</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Thruway</t>
+          <t>Township Road</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="B681" t="inlineStr">
         <is>
-          <t>Timber Road</t>
+          <t>Trace</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Timber Road</t>
+          <t>Trace</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="B682" t="inlineStr">
         <is>
-          <t>Townline</t>
+          <t>Track</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Townline</t>
+          <t>Track</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="B683" t="inlineStr">
         <is>
-          <t>Town Road</t>
+          <t>Trafficway</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Town Road</t>
+          <t>Trafficway</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="B684" t="inlineStr">
         <is>
-          <t>Township Road</t>
+          <t>Trail</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Township Road</t>
+          <t>Trail</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="B685" t="inlineStr">
         <is>
-          <t>Trace</t>
+          <t>Trailer</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Trace</t>
+          <t>Trailer</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="B686" t="inlineStr">
         <is>
-          <t>Track</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Track</t>
+          <t>Triangle</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="B687" t="inlineStr">
         <is>
-          <t>Trafficway</t>
+          <t>Truck Trail</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Trafficway</t>
+          <t>Truck Trail</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="B688" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Tunnel</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Tunnel</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="B689" t="inlineStr">
         <is>
-          <t>Trailer</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Trailer</t>
+          <t>Turn</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="B690" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Turnpike</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Turnpike</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="B691" t="inlineStr">
         <is>
-          <t>Truck Trail</t>
+          <t>United States Forest Service Road</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Truck Trail</t>
+          <t>United States Forest Service Road</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="B692" t="inlineStr">
         <is>
-          <t>Tunnel</t>
+          <t>United States Highway</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Tunnel</t>
+          <t>United States Highway</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="B693" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Underpass</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Underpass</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="B694" t="inlineStr">
         <is>
-          <t>Turnpike</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Turnpike</t>
+          <t>Union</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="B695" t="inlineStr">
         <is>
-          <t>United States Forest Service Road</t>
+          <t>Unions</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>United States Forest Service Road</t>
+          <t>Unions</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="B696" t="inlineStr">
         <is>
-          <t>United States Highway</t>
+          <t>Uunye</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>United States Highway</t>
+          <t>Uunye</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="B697" t="inlineStr">
         <is>
-          <t>Underpass</t>
+          <t>Valley</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Underpass</t>
+          <t>Valley</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="B698" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Valleys</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Valleys</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="B699" t="inlineStr">
         <is>
-          <t>Unions</t>
+          <t>Via</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Unions</t>
+          <t>Via</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="B700" t="inlineStr">
         <is>
-          <t>Uunye</t>
+          <t>Viaduct</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Uunye</t>
+          <t>Viaduct</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="B701" t="inlineStr">
         <is>
-          <t>Valley</t>
+          <t>View</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Valley</t>
+          <t>View</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="B702" t="inlineStr">
         <is>
-          <t>Valleys</t>
+          <t>Views</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Valleys</t>
+          <t>Views</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="B703" t="inlineStr">
         <is>
-          <t>Via</t>
+          <t>Villa</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Via</t>
+          <t>Villa</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="B704" t="inlineStr">
         <is>
-          <t>Viaduct</t>
+          <t>Village</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Viaduct</t>
+          <t>Village</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="B705" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Villages</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Villages</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="B706" t="inlineStr">
         <is>
-          <t>Views</t>
+          <t>Ville</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Views</t>
+          <t>Ville</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="B707" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Vista</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Vista</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="B708" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Vog</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Village</t>
+          <t>Vog</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="B709" t="inlineStr">
         <is>
-          <t>Villages</t>
+          <t>Waddy</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Villages</t>
+          <t>Waddy</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="B710" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Walk</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Ville</t>
+          <t>Walk</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="B711" t="inlineStr">
         <is>
-          <t>Vista</t>
+          <t>Walks</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Vista</t>
+          <t>Walks</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="B712" t="inlineStr">
         <is>
-          <t>Vog</t>
+          <t>Wall</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Vog</t>
+          <t>Wall</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="B713" t="inlineStr">
         <is>
-          <t>Waddy</t>
+          <t>Way</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Waddy</t>
+          <t>Way</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="B714" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Ways</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Walk</t>
+          <t>Ways</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="B715" t="inlineStr">
         <is>
-          <t>Walks</t>
+          <t>Weeg</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Walks</t>
+          <t>Weeg</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="B716" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Well</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Well</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="B717" t="inlineStr">
         <is>
-          <t>Way</t>
+          <t>Wells</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Way</t>
+          <t>Wells</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="B718" t="inlineStr">
         <is>
-          <t>Ways</t>
+          <t>Woods</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Ways</t>
+          <t>Woods</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="B719" t="inlineStr">
         <is>
-          <t>Weeg</t>
+          <t>Wye</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Weeg</t>
+          <t>Wye</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="B720" t="inlineStr">
         <is>
-          <t>Well</t>
+          <t>Wynd</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Well</t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="B721" t="inlineStr">
-        <is>
-          <t>Wells</t>
-        </is>
-      </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>Wells</t>
+          <t>Wynd</t>
         </is>
       </c>
     </row>
     <row r="722">
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>Woods</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>Woods</t>
+      <c r="A722" s="6" t="inlineStr">
+        <is>
+          <t>StreetNamePreTypeSeparator</t>
+        </is>
+      </c>
+      <c r="B722" s="6" t="inlineStr">
+        <is>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="C722" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D722" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A preposition or prepositional phrase between the Street Name Pre Type and the Street Name.
+</t>
         </is>
       </c>
     </row>
     <row r="723">
-      <c r="B723" t="inlineStr">
-        <is>
-          <t>Wye</t>
-        </is>
-      </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>Wye</t>
+      <c r="B723" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C723" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="B724" t="inlineStr">
         <is>
-          <t>Wynd</t>
+          <t>of the</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Wynd</t>
+          <t>of the</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>at</t>
         </is>
       </c>
     </row>
     <row r="726">
-      <c r="A726" s="6" t="inlineStr">
-        <is>
-          <t>StreetNamePreTypeSeparator</t>
-        </is>
-      </c>
-      <c r="B726" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C726" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D726" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A preposition or prepositional phrase between the Street Name Pre Type and the Street Name.
-</t>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="727">
-      <c r="B727" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C727" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>de la</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>de la</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="B728" t="inlineStr">
         <is>
-          <t>of the</t>
+          <t>del</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>of the</t>
+          <t>del</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="B729" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>de las</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>de las</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="B730" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>des</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>des</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="B731" t="inlineStr">
         <is>
-          <t>de la</t>
+          <t>in the</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>de la</t>
+          <t>in the</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="B732" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>to the</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>to the</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="B733" t="inlineStr">
         <is>
-          <t>de las</t>
+          <t>of</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>de las</t>
+          <t>of</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="B734" t="inlineStr">
         <is>
-          <t>des</t>
+          <t>on the</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>des</t>
+          <t>on the</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="B735" t="inlineStr">
         <is>
-          <t>in the</t>
+          <t>to</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>in the</t>
-        </is>
-      </c>
-    </row>
-    <row r="736">
-      <c r="B736" t="inlineStr">
-        <is>
-          <t>to the</t>
-        </is>
-      </c>
-      <c r="C736" t="inlineStr">
-        <is>
-          <t>to the</t>
+          <t>to</t>
         </is>
       </c>
     </row>
     <row r="737">
-      <c r="B737" t="inlineStr">
-        <is>
-          <t>of</t>
-        </is>
-      </c>
-      <c r="C737" t="inlineStr">
-        <is>
-          <t>of</t>
+      <c r="A737" s="6" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B737" s="6" t="inlineStr">
+        <is>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="C737" s="6" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D737" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicates if the address range of the road segment, relative to the FROM node, should be used for civic location validation.
+</t>
         </is>
       </c>
     </row>
     <row r="738">
-      <c r="B738" t="inlineStr">
-        <is>
-          <t>on the</t>
-        </is>
-      </c>
-      <c r="C738" t="inlineStr">
-        <is>
-          <t>on the</t>
+      <c r="B738" s="1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C738" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="B739" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>to</t>
-        </is>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" s="6" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B741" s="6" t="inlineStr">
-        <is>
-          <t>CODED</t>
-        </is>
-      </c>
-      <c r="C741" s="6" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="D741" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indicates if the address range of the road segment, relative to the FROM node, should be used for civic location validation.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="742">
-      <c r="B742" s="1" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="C742" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="743">
-      <c r="B743" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C743" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="B744" t="inlineStr">
+    <row r="740">
+      <c r="B740" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr">
+      <c r="C740" t="inlineStr">
         <is>
           <t>No</t>
         </is>
